--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -4903,11 +4903,11 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H60" s="5">
         <f>IF(G60="","",TODAY()-G60)</f>
@@ -4915,11 +4915,11 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
@@ -4978,11 +4978,11 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H61" s="5">
         <f>IF(G61="","",TODAY()-G61)</f>
@@ -4990,11 +4990,11 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
@@ -5053,11 +5053,11 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H62" s="5">
         <f>IF(G62="","",TODAY()-G62)</f>
@@ -5065,11 +5065,11 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
@@ -5128,11 +5128,11 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H63" s="5">
         <f>IF(G63="","",TODAY()-G63)</f>
@@ -5140,11 +5140,11 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
@@ -5203,11 +5203,11 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H64" s="5">
         <f>IF(G64="","",TODAY()-G64)</f>
@@ -5215,11 +5215,11 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
@@ -5278,11 +5278,11 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H65" s="5">
         <f>IF(G65="","",TODAY()-G65)</f>
@@ -5290,11 +5290,11 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
@@ -5422,11 +5422,11 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H67" s="5">
         <f>IF(G67="","",TODAY()-G67)</f>
@@ -5434,11 +5434,11 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G68" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H68" s="5">
         <f>IF(G68="","",TODAY()-G68)</f>
@@ -5509,11 +5509,11 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H69" s="5">
         <f>IF(G69="","",TODAY()-G69)</f>
@@ -5584,11 +5584,11 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J69" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -5647,11 +5647,11 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H70" s="5">
         <f>IF(G70="","",TODAY()-G70)</f>
@@ -5659,11 +5659,11 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J70" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
@@ -5722,11 +5722,11 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H71" s="5">
         <f>IF(G71="","",TODAY()-G71)</f>
@@ -5734,11 +5734,11 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -5797,11 +5797,11 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H72" s="5">
         <f>IF(G72="","",TODAY()-G72)</f>
@@ -5809,11 +5809,11 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H73" s="5">
         <f>IF(G73="","",TODAY()-G73)</f>
@@ -5884,11 +5884,11 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Opted Out</t>
         </is>
       </c>
       <c r="G74" s="6" t="n">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J74" s="6" t="n">
@@ -5973,10 +5973,12 @@
       <c r="L74" s="6" t="n"/>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N74" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>46274</v>
+      </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5990,7 +5992,7 @@
       </c>
       <c r="R74" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative (Software Sales) role at Makunai Global | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Business Development Representative (Software Sales) role at Makunai Global | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | Replied "Thanks, but I'm not interested." 2026-09-04 (caught during Wed 2026-09-09 FU3 run) -&gt; Opted Out, excluded from send.</t>
         </is>
       </c>
     </row>
@@ -6091,11 +6093,11 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H76" s="5">
         <f>IF(G76="","",TODAY()-G76)</f>
@@ -6103,11 +6105,11 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J76" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
@@ -6166,11 +6168,11 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H77" s="5">
         <f>IF(G77="","",TODAY()-G77)</f>
@@ -6178,11 +6180,11 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J77" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
@@ -6310,11 +6312,11 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H79" s="5">
         <f>IF(G79="","",TODAY()-G79)</f>
@@ -6322,11 +6324,11 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J79" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
@@ -6385,11 +6387,11 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H80" s="5">
         <f>IF(G80="","",TODAY()-G80)</f>
@@ -6397,11 +6399,11 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J80" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
@@ -6744,11 +6746,11 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H85" s="5">
         <f>IF(G85="","",TODAY()-G85)</f>
@@ -6756,11 +6758,11 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J85" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
@@ -6888,11 +6890,11 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H87" s="5">
         <f>IF(G87="","",TODAY()-G87)</f>
@@ -6900,11 +6902,11 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J87" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
@@ -6963,11 +6965,11 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H88" s="5">
         <f>IF(G88="","",TODAY()-G88)</f>
@@ -6975,11 +6977,11 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J88" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
@@ -7038,11 +7040,11 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H89" s="5">
         <f>IF(G89="","",TODAY()-G89)</f>
@@ -7050,11 +7052,11 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J89" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
@@ -7113,11 +7115,11 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H90" s="5">
         <f>IF(G90="","",TODAY()-G90)</f>
@@ -7125,11 +7127,11 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J90" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
@@ -7265,11 +7267,11 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H92" s="5">
         <f>IF(G92="","",TODAY()-G92)</f>
@@ -7277,11 +7279,11 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J92" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
@@ -7417,11 +7419,11 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H94" s="5">
         <f>IF(G94="","",TODAY()-G94)</f>
@@ -7429,11 +7431,11 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J94" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
@@ -7492,11 +7494,11 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H95" s="5">
         <f>IF(G95="","",TODAY()-G95)</f>
@@ -7504,11 +7506,11 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J95" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
@@ -7567,11 +7569,11 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G96" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H96" s="5">
         <f>IF(G96="","",TODAY()-G96)</f>
@@ -7579,11 +7581,11 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J96" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
@@ -7642,11 +7644,11 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G97" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H97" s="5">
         <f>IF(G97="","",TODAY()-G97)</f>
@@ -7654,11 +7656,11 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J97" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
@@ -7717,11 +7719,11 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H98" s="5">
         <f>IF(G98="","",TODAY()-G98)</f>
@@ -7729,11 +7731,11 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J98" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
@@ -7792,11 +7794,11 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G99" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H99" s="5">
         <f>IF(G99="","",TODAY()-G99)</f>
@@ -7804,11 +7806,11 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J99" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
@@ -7944,11 +7946,11 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H101" s="5">
         <f>IF(G101="","",TODAY()-G101)</f>
@@ -7956,11 +7958,11 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J101" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
@@ -8173,11 +8175,11 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G104" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H104" s="5">
         <f>IF(G104="","",TODAY()-G104)</f>
@@ -8185,11 +8187,11 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J104" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
@@ -8248,11 +8250,11 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G105" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H105" s="5">
         <f>IF(G105="","",TODAY()-G105)</f>
@@ -8260,11 +8262,11 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J105" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
@@ -8477,11 +8479,11 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H108" s="5">
         <f>IF(G108="","",TODAY()-G108)</f>
@@ -8489,11 +8491,11 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J108" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
@@ -8552,11 +8554,11 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G109" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H109" s="5">
         <f>IF(G109="","",TODAY()-G109)</f>
@@ -8564,11 +8566,11 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J109" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
@@ -8627,11 +8629,11 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H110" s="5">
         <f>IF(G110="","",TODAY()-G110)</f>
@@ -8639,11 +8641,11 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J110" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
@@ -8702,11 +8704,11 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 2 Sent</t>
+          <t>Follow-up 3 Sent</t>
         </is>
       </c>
       <c r="G111" s="6" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H111" s="5">
         <f>IF(G111="","",TODAY()-G111)</f>
@@ -8714,11 +8716,11 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 3</t>
+          <t>Send Follow-up 4</t>
         </is>
       </c>
       <c r="J111" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -4903,11 +4903,11 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H60" s="5">
         <f>IF(G60="","",TODAY()-G60)</f>
@@ -4915,12 +4915,10 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="n"/>
       <c r="K60" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4946,7 +4944,7 @@
       </c>
       <c r="R60" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead role at adidas | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead role at adidas | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -4978,11 +4976,11 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H61" s="5">
         <f>IF(G61="","",TODAY()-G61)</f>
@@ -4990,12 +4988,10 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n"/>
       <c r="K61" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5021,7 +5017,7 @@
       </c>
       <c r="R61" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Manager role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Manager role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5053,11 +5049,11 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H62" s="5">
         <f>IF(G62="","",TODAY()-G62)</f>
@@ -5065,12 +5061,10 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="n"/>
       <c r="K62" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5096,7 +5090,7 @@
       </c>
       <c r="R62" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales &amp; Business Development Representative role at Zvolv | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Sales &amp; Business Development Representative role at Zvolv | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5128,11 +5122,11 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H63" s="5">
         <f>IF(G63="","",TODAY()-G63)</f>
@@ -5140,12 +5134,10 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="n"/>
       <c r="K63" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5171,7 +5163,7 @@
       </c>
       <c r="R63" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative - Sales role at TopSource | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Business Development Representative - Sales role at TopSource | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5203,11 +5195,11 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H64" s="5">
         <f>IF(G64="","",TODAY()-G64)</f>
@@ -5215,12 +5207,10 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="n"/>
       <c r="K64" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5246,7 +5236,7 @@
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at Atos | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Consultant role at Atos | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5278,11 +5268,11 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H65" s="5">
         <f>IF(G65="","",TODAY()-G65)</f>
@@ -5290,12 +5280,10 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="n"/>
       <c r="K65" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5321,7 +5309,7 @@
       </c>
       <c r="R65" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at BT Group | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Consultant role at BT Group | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5422,11 +5410,11 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H67" s="5">
         <f>IF(G67="","",TODAY()-G67)</f>
@@ -5434,12 +5422,10 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n"/>
       <c r="K67" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5465,7 +5451,7 @@
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Consultant role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5497,11 +5483,11 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G68" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H68" s="5">
         <f>IF(G68="","",TODAY()-G68)</f>
@@ -5509,12 +5495,10 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n"/>
       <c r="K68" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5540,7 +5524,7 @@
       </c>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant - Delivery Lead role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Consultant - Delivery Lead role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5572,11 +5556,11 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G69" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H69" s="5">
         <f>IF(G69="","",TODAY()-G69)</f>
@@ -5584,12 +5568,10 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="n"/>
       <c r="K69" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5615,7 +5597,7 @@
       </c>
       <c r="R69" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant role at Northern Trust | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Consultant role at Northern Trust | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5647,11 +5629,11 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G70" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H70" s="5">
         <f>IF(G70="","",TODAY()-G70)</f>
@@ -5659,12 +5641,10 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="n"/>
       <c r="K70" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5690,7 +5670,7 @@
       </c>
       <c r="R70" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Executive role at Capgemini | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Executive role at Capgemini | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5722,11 +5702,11 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G71" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H71" s="5">
         <f>IF(G71="","",TODAY()-G71)</f>
@@ -5734,12 +5714,10 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="n"/>
       <c r="K71" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5765,7 +5743,7 @@
       </c>
       <c r="R71" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative role at Insight | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Business Development Representative role at Insight | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5797,11 +5775,11 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H72" s="5">
         <f>IF(G72="","",TODAY()-G72)</f>
@@ -5809,12 +5787,10 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="n"/>
       <c r="K72" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5840,7 +5816,7 @@
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -5872,11 +5848,11 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G73" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H73" s="5">
         <f>IF(G73="","",TODAY()-G73)</f>
@@ -5884,12 +5860,10 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n"/>
       <c r="K73" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5915,7 +5889,7 @@
       </c>
       <c r="R73" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant Delivery-Lead role at Worldline Global Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Consultant Delivery-Lead role at Worldline Global Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -6093,11 +6067,11 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G76" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H76" s="5">
         <f>IF(G76="","",TODAY()-G76)</f>
@@ -6105,12 +6079,10 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="n"/>
       <c r="K76" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -6136,7 +6108,7 @@
       </c>
       <c r="R76" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at LHH | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at LHH | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -6168,11 +6140,11 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G77" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H77" s="5">
         <f>IF(G77="","",TODAY()-G77)</f>
@@ -6180,12 +6152,10 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="n"/>
       <c r="K77" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -6211,7 +6181,7 @@
       </c>
       <c r="R77" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -6312,11 +6282,11 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G79" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H79" s="5">
         <f>IF(G79="","",TODAY()-G79)</f>
@@ -6324,12 +6294,10 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J79" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="n"/>
       <c r="K79" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -6355,7 +6323,7 @@
       </c>
       <c r="R79" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Senior Delivery Manager role at EPAM Systems | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Senior Delivery Manager role at EPAM Systems | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -6387,11 +6355,11 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G80" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H80" s="5">
         <f>IF(G80="","",TODAY()-G80)</f>
@@ -6399,12 +6367,10 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J80" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="n"/>
       <c r="K80" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -6430,7 +6396,7 @@
       </c>
       <c r="R80" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -6746,11 +6712,11 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G85" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H85" s="5">
         <f>IF(G85="","",TODAY()-G85)</f>
@@ -6758,12 +6724,10 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="n"/>
       <c r="K85" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -6789,7 +6753,7 @@
       </c>
       <c r="R85" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -6890,11 +6854,11 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H87" s="5">
         <f>IF(G87="","",TODAY()-G87)</f>
@@ -6902,12 +6866,10 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="n"/>
       <c r="K87" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -6933,7 +6895,7 @@
       </c>
       <c r="R87" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -6965,11 +6927,11 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H88" s="5">
         <f>IF(G88="","",TODAY()-G88)</f>
@@ -6977,12 +6939,10 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J88" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="n"/>
       <c r="K88" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7008,7 +6968,7 @@
       </c>
       <c r="R88" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7040,11 +7000,11 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H89" s="5">
         <f>IF(G89="","",TODAY()-G89)</f>
@@ -7052,12 +7012,10 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J89" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="n"/>
       <c r="K89" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7083,7 +7041,7 @@
       </c>
       <c r="R89" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7115,11 +7073,11 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H90" s="5">
         <f>IF(G90="","",TODAY()-G90)</f>
@@ -7127,12 +7085,10 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J90" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="n"/>
       <c r="K90" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7158,7 +7114,7 @@
       </c>
       <c r="R90" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7267,11 +7223,11 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H92" s="5">
         <f>IF(G92="","",TODAY()-G92)</f>
@@ -7279,12 +7235,10 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J92" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="n"/>
       <c r="K92" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7310,7 +7264,7 @@
       </c>
       <c r="R92" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7419,11 +7373,11 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H94" s="5">
         <f>IF(G94="","",TODAY()-G94)</f>
@@ -7431,12 +7385,10 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J94" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="n"/>
       <c r="K94" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7462,7 +7414,7 @@
       </c>
       <c r="R94" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7494,11 +7446,11 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H95" s="5">
         <f>IF(G95="","",TODAY()-G95)</f>
@@ -7506,12 +7458,10 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J95" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="n"/>
       <c r="K95" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7537,7 +7487,7 @@
       </c>
       <c r="R95" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7569,11 +7519,11 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G96" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H96" s="5">
         <f>IF(G96="","",TODAY()-G96)</f>
@@ -7581,12 +7531,10 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J96" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="n"/>
       <c r="K96" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7612,7 +7560,7 @@
       </c>
       <c r="R96" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7644,11 +7592,11 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G97" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H97" s="5">
         <f>IF(G97="","",TODAY()-G97)</f>
@@ -7656,12 +7604,10 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="n"/>
       <c r="K97" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7687,7 +7633,7 @@
       </c>
       <c r="R97" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Service Delivery Manager role at V &amp; V Comptech Systems Private Limited | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Service Delivery Manager role at V &amp; V Comptech Systems Private Limited | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7719,11 +7665,11 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H98" s="5">
         <f>IF(G98="","",TODAY()-G98)</f>
@@ -7731,12 +7677,10 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J98" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="n"/>
       <c r="K98" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7762,7 +7706,7 @@
       </c>
       <c r="R98" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7794,11 +7738,11 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G99" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H99" s="5">
         <f>IF(G99="","",TODAY()-G99)</f>
@@ -7806,12 +7750,10 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J99" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="n"/>
       <c r="K99" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7837,7 +7779,7 @@
       </c>
       <c r="R99" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -7946,11 +7888,11 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H101" s="5">
         <f>IF(G101="","",TODAY()-G101)</f>
@@ -7958,12 +7900,10 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J101" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="n"/>
       <c r="K101" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7989,7 +7929,7 @@
       </c>
       <c r="R101" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -8175,11 +8115,11 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G104" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H104" s="5">
         <f>IF(G104="","",TODAY()-G104)</f>
@@ -8187,12 +8127,10 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J104" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="n"/>
       <c r="K104" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -8218,7 +8156,7 @@
       </c>
       <c r="R104" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -8250,11 +8188,11 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G105" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H105" s="5">
         <f>IF(G105="","",TODAY()-G105)</f>
@@ -8262,12 +8200,10 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J105" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="n"/>
       <c r="K105" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -8293,7 +8229,7 @@
       </c>
       <c r="R105" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -8479,11 +8415,11 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H108" s="5">
         <f>IF(G108="","",TODAY()-G108)</f>
@@ -8491,12 +8427,10 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J108" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="n"/>
       <c r="K108" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -8522,7 +8456,7 @@
       </c>
       <c r="R108" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Lead Consultant role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -8554,11 +8488,11 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G109" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H109" s="5">
         <f>IF(G109="","",TODAY()-G109)</f>
@@ -8566,12 +8500,10 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J109" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="n"/>
       <c r="K109" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -8597,7 +8529,7 @@
       </c>
       <c r="R109" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Manager (Consultant) - Senior Delivery Lead role at Burendo | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Delivery Manager (Consultant) - Senior Delivery Lead role at Burendo | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -8629,11 +8561,11 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H110" s="5">
         <f>IF(G110="","",TODAY()-G110)</f>
@@ -8641,12 +8573,10 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J110" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="n"/>
       <c r="K110" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -8672,7 +8602,7 @@
       </c>
       <c r="R110" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Agile Delivery Manager role at tombola | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Agile Delivery Manager role at tombola | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>
@@ -8704,11 +8634,11 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Follow-up 3 Sent</t>
+          <t>Sequence Complete</t>
         </is>
       </c>
       <c r="G111" s="6" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="H111" s="5">
         <f>IF(G111="","",TODAY()-G111)</f>
@@ -8716,12 +8646,10 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Send Follow-up 4</t>
-        </is>
-      </c>
-      <c r="J111" s="6" t="n">
-        <v>46276</v>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="n"/>
       <c r="K111" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -8747,7 +8675,7 @@
       </c>
       <c r="R111" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales and Business Development Representative role at Cygnus Group Ltd | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31)</t>
+          <t>Hook: Saw your Sales and Business Development Representative role at Cygnus Group Ltd | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8680,1154 +8680,3754 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n"/>
-      <c r="B112" s="5" t="n"/>
-      <c r="C112" s="5" t="n"/>
-      <c r="D112" s="5" t="n"/>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="5" t="n"/>
-      <c r="G112" s="6" t="n"/>
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Yuvika Sharma</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>yuvika.sharma@tecnotree.com</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/yuvika-sharma-3370b6147</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H112" s="5">
         <f>IF(G112="","",TODAY()-G112)</f>
         <v/>
       </c>
-      <c r="I112" s="5" t="n"/>
-      <c r="J112" s="6" t="n"/>
-      <c r="K112" s="5" t="n"/>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L112" s="6" t="n"/>
-      <c r="M112" s="5" t="n"/>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N112" s="6" t="n"/>
-      <c r="O112" s="5" t="n"/>
+      <c r="O112" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P112" s="6" t="n"/>
-      <c r="Q112" s="5" t="n"/>
-      <c r="R112" s="5" t="n"/>
+      <c r="Q112" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R112" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n"/>
-      <c r="B113" s="5" t="n"/>
-      <c r="C113" s="5" t="n"/>
-      <c r="D113" s="5" t="n"/>
-      <c r="E113" s="5" t="n"/>
-      <c r="F113" s="5" t="n"/>
-      <c r="G113" s="6" t="n"/>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Pratiksha Kulkarni</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>pratiksha.kulkarni@solytics-partners.com</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/pratiksha-kulkarni-615139148</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H113" s="5">
         <f>IF(G113="","",TODAY()-G113)</f>
         <v/>
       </c>
-      <c r="I113" s="5" t="n"/>
-      <c r="J113" s="6" t="n"/>
-      <c r="K113" s="5" t="n"/>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L113" s="6" t="n"/>
-      <c r="M113" s="5" t="n"/>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N113" s="6" t="n"/>
-      <c r="O113" s="5" t="n"/>
+      <c r="O113" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P113" s="6" t="n"/>
-      <c r="Q113" s="5" t="n"/>
-      <c r="R113" s="5" t="n"/>
+      <c r="Q113" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n"/>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="5" t="n"/>
-      <c r="D114" s="5" t="n"/>
-      <c r="E114" s="5" t="n"/>
-      <c r="F114" s="5" t="n"/>
-      <c r="G114" s="6" t="n"/>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Esha Gulati</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>esha.gulati@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/esha-gulati</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H114" s="5">
         <f>IF(G114="","",TODAY()-G114)</f>
         <v/>
       </c>
-      <c r="I114" s="5" t="n"/>
-      <c r="J114" s="6" t="n"/>
-      <c r="K114" s="5" t="n"/>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L114" s="6" t="n"/>
-      <c r="M114" s="5" t="n"/>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N114" s="6" t="n"/>
-      <c r="O114" s="5" t="n"/>
+      <c r="O114" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P114" s="6" t="n"/>
-      <c r="Q114" s="5" t="n"/>
-      <c r="R114" s="5" t="n"/>
+      <c r="Q114" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R114" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n"/>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="5" t="n"/>
-      <c r="F115" s="5" t="n"/>
-      <c r="G115" s="6" t="n"/>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Sharvari Rao</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>sharvari.rao@ptrglobal.com</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sharvari-rao-711b6a1a2</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H115" s="5">
         <f>IF(G115="","",TODAY()-G115)</f>
         <v/>
       </c>
-      <c r="I115" s="5" t="n"/>
-      <c r="J115" s="6" t="n"/>
-      <c r="K115" s="5" t="n"/>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L115" s="6" t="n"/>
-      <c r="M115" s="5" t="n"/>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N115" s="6" t="n"/>
-      <c r="O115" s="5" t="n"/>
+      <c r="O115" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P115" s="6" t="n"/>
-      <c r="Q115" s="5" t="n"/>
-      <c r="R115" s="5" t="n"/>
+      <c r="Q115" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n"/>
-      <c r="B116" s="5" t="n"/>
-      <c r="C116" s="5" t="n"/>
-      <c r="D116" s="5" t="n"/>
-      <c r="E116" s="5" t="n"/>
-      <c r="F116" s="5" t="n"/>
-      <c r="G116" s="6" t="n"/>
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Bhushan Raut</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>bhushan.r@indictranstech.com</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/bhushanraut43</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H116" s="5">
         <f>IF(G116="","",TODAY()-G116)</f>
         <v/>
       </c>
-      <c r="I116" s="5" t="n"/>
-      <c r="J116" s="6" t="n"/>
-      <c r="K116" s="5" t="n"/>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L116" s="6" t="n"/>
-      <c r="M116" s="5" t="n"/>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N116" s="6" t="n"/>
-      <c r="O116" s="5" t="n"/>
+      <c r="O116" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P116" s="6" t="n"/>
-      <c r="Q116" s="5" t="n"/>
-      <c r="R116" s="5" t="n"/>
+      <c r="Q116" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n"/>
-      <c r="B117" s="5" t="n"/>
-      <c r="C117" s="5" t="n"/>
-      <c r="D117" s="5" t="n"/>
-      <c r="E117" s="5" t="n"/>
-      <c r="F117" s="5" t="n"/>
-      <c r="G117" s="6" t="n"/>
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Ambarish Khound</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>ambarish.khound@metricstream.com</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ambarishkhound</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H117" s="5">
         <f>IF(G117="","",TODAY()-G117)</f>
         <v/>
       </c>
-      <c r="I117" s="5" t="n"/>
-      <c r="J117" s="6" t="n"/>
-      <c r="K117" s="5" t="n"/>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L117" s="6" t="n"/>
-      <c r="M117" s="5" t="n"/>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N117" s="6" t="n"/>
-      <c r="O117" s="5" t="n"/>
+      <c r="O117" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P117" s="6" t="n"/>
-      <c r="Q117" s="5" t="n"/>
-      <c r="R117" s="5" t="n"/>
+      <c r="Q117" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n"/>
-      <c r="B118" s="5" t="n"/>
-      <c r="C118" s="5" t="n"/>
-      <c r="D118" s="5" t="n"/>
-      <c r="E118" s="5" t="n"/>
-      <c r="F118" s="5" t="n"/>
-      <c r="G118" s="6" t="n"/>
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Vikash Meena</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>vikash.meena@photon.com</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/iamvikash96</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H118" s="5">
         <f>IF(G118="","",TODAY()-G118)</f>
         <v/>
       </c>
-      <c r="I118" s="5" t="n"/>
-      <c r="J118" s="6" t="n"/>
-      <c r="K118" s="5" t="n"/>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L118" s="6" t="n"/>
-      <c r="M118" s="5" t="n"/>
+      <c r="M118" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N118" s="6" t="n"/>
-      <c r="O118" s="5" t="n"/>
+      <c r="O118" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P118" s="6" t="n"/>
-      <c r="Q118" s="5" t="n"/>
-      <c r="R118" s="5" t="n"/>
+      <c r="Q118" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R118" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n"/>
-      <c r="B119" s="5" t="n"/>
-      <c r="C119" s="5" t="n"/>
-      <c r="D119" s="5" t="n"/>
-      <c r="E119" s="5" t="n"/>
-      <c r="F119" s="5" t="n"/>
-      <c r="G119" s="6" t="n"/>
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Himani Ahuja</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>himani.ahuja@solytics-partners.com</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/himani-ahuja-532a39233</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H119" s="5">
         <f>IF(G119="","",TODAY()-G119)</f>
         <v/>
       </c>
-      <c r="I119" s="5" t="n"/>
-      <c r="J119" s="6" t="n"/>
-      <c r="K119" s="5" t="n"/>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L119" s="6" t="n"/>
-      <c r="M119" s="5" t="n"/>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N119" s="6" t="n"/>
-      <c r="O119" s="5" t="n"/>
+      <c r="O119" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P119" s="6" t="n"/>
-      <c r="Q119" s="5" t="n"/>
-      <c r="R119" s="5" t="n"/>
+      <c r="Q119" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R119" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n"/>
-      <c r="B120" s="5" t="n"/>
-      <c r="C120" s="5" t="n"/>
-      <c r="D120" s="5" t="n"/>
-      <c r="E120" s="5" t="n"/>
-      <c r="F120" s="5" t="n"/>
-      <c r="G120" s="6" t="n"/>
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Manav Juneja</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>manav.juneja@infojiniconsulting.com</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/manavjuneja84</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H120" s="5">
         <f>IF(G120="","",TODAY()-G120)</f>
         <v/>
       </c>
-      <c r="I120" s="5" t="n"/>
-      <c r="J120" s="6" t="n"/>
-      <c r="K120" s="5" t="n"/>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L120" s="6" t="n"/>
-      <c r="M120" s="5" t="n"/>
+      <c r="M120" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N120" s="6" t="n"/>
-      <c r="O120" s="5" t="n"/>
+      <c r="O120" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P120" s="6" t="n"/>
-      <c r="Q120" s="5" t="n"/>
-      <c r="R120" s="5" t="n"/>
+      <c r="Q120" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R120" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n"/>
-      <c r="B121" s="5" t="n"/>
-      <c r="C121" s="5" t="n"/>
-      <c r="D121" s="5" t="n"/>
-      <c r="E121" s="5" t="n"/>
-      <c r="F121" s="5" t="n"/>
-      <c r="G121" s="6" t="n"/>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Krishna Kulkarni</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>kulkarnik@hcl.com</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/krishna-k9</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H121" s="5">
         <f>IF(G121="","",TODAY()-G121)</f>
         <v/>
       </c>
-      <c r="I121" s="5" t="n"/>
-      <c r="J121" s="6" t="n"/>
-      <c r="K121" s="5" t="n"/>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L121" s="6" t="n"/>
-      <c r="M121" s="5" t="n"/>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N121" s="6" t="n"/>
-      <c r="O121" s="5" t="n"/>
+      <c r="O121" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P121" s="6" t="n"/>
-      <c r="Q121" s="5" t="n"/>
-      <c r="R121" s="5" t="n"/>
+      <c r="Q121" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R121" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n"/>
-      <c r="B122" s="5" t="n"/>
-      <c r="C122" s="5" t="n"/>
-      <c r="D122" s="5" t="n"/>
-      <c r="E122" s="5" t="n"/>
-      <c r="F122" s="5" t="n"/>
-      <c r="G122" s="6" t="n"/>
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Shivani Singh</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>shivani.singh@incitegravity.com</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shivani-singh2815</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H122" s="5">
         <f>IF(G122="","",TODAY()-G122)</f>
         <v/>
       </c>
-      <c r="I122" s="5" t="n"/>
-      <c r="J122" s="6" t="n"/>
-      <c r="K122" s="5" t="n"/>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L122" s="6" t="n"/>
-      <c r="M122" s="5" t="n"/>
+      <c r="M122" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N122" s="6" t="n"/>
-      <c r="O122" s="5" t="n"/>
+      <c r="O122" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P122" s="6" t="n"/>
-      <c r="Q122" s="5" t="n"/>
-      <c r="R122" s="5" t="n"/>
+      <c r="Q122" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R122" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n"/>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="5" t="n"/>
-      <c r="D123" s="5" t="n"/>
-      <c r="E123" s="5" t="n"/>
-      <c r="F123" s="5" t="n"/>
-      <c r="G123" s="6" t="n"/>
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Sumit Tyagi</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>sumit.tyagi3@wipro.com</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sumit-tyagi-7aa00562</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H123" s="5">
         <f>IF(G123="","",TODAY()-G123)</f>
         <v/>
       </c>
-      <c r="I123" s="5" t="n"/>
-      <c r="J123" s="6" t="n"/>
-      <c r="K123" s="5" t="n"/>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L123" s="6" t="n"/>
-      <c r="M123" s="5" t="n"/>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N123" s="6" t="n"/>
-      <c r="O123" s="5" t="n"/>
+      <c r="O123" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P123" s="6" t="n"/>
-      <c r="Q123" s="5" t="n"/>
-      <c r="R123" s="5" t="n"/>
+      <c r="Q123" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R123" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n"/>
-      <c r="B124" s="5" t="n"/>
-      <c r="C124" s="5" t="n"/>
-      <c r="D124" s="5" t="n"/>
-      <c r="E124" s="5" t="n"/>
-      <c r="F124" s="5" t="n"/>
-      <c r="G124" s="6" t="n"/>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Animesh Anand</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>animesha@maqsoftware.com</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/animesh-anand-mba</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H124" s="5">
         <f>IF(G124="","",TODAY()-G124)</f>
         <v/>
       </c>
-      <c r="I124" s="5" t="n"/>
-      <c r="J124" s="6" t="n"/>
-      <c r="K124" s="5" t="n"/>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L124" s="6" t="n"/>
-      <c r="M124" s="5" t="n"/>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N124" s="6" t="n"/>
-      <c r="O124" s="5" t="n"/>
+      <c r="O124" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P124" s="6" t="n"/>
-      <c r="Q124" s="5" t="n"/>
-      <c r="R124" s="5" t="n"/>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R124" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n"/>
-      <c r="B125" s="5" t="n"/>
-      <c r="C125" s="5" t="n"/>
-      <c r="D125" s="5" t="n"/>
-      <c r="E125" s="5" t="n"/>
-      <c r="F125" s="5" t="n"/>
-      <c r="G125" s="6" t="n"/>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Himanshu Shende</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>himanshu.shende@wipro.com</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/himanshu-shende55555</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H125" s="5">
         <f>IF(G125="","",TODAY()-G125)</f>
         <v/>
       </c>
-      <c r="I125" s="5" t="n"/>
-      <c r="J125" s="6" t="n"/>
-      <c r="K125" s="5" t="n"/>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L125" s="6" t="n"/>
-      <c r="M125" s="5" t="n"/>
+      <c r="M125" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N125" s="6" t="n"/>
-      <c r="O125" s="5" t="n"/>
+      <c r="O125" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P125" s="6" t="n"/>
-      <c r="Q125" s="5" t="n"/>
-      <c r="R125" s="5" t="n"/>
+      <c r="Q125" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R125" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n"/>
-      <c r="B126" s="5" t="n"/>
-      <c r="C126" s="5" t="n"/>
-      <c r="D126" s="5" t="n"/>
-      <c r="E126" s="5" t="n"/>
-      <c r="F126" s="5" t="n"/>
-      <c r="G126" s="6" t="n"/>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Akanksha Barnwal</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>akanksha.b@infosys.com</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/akanksha-barnwal-84b082114</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H126" s="5">
         <f>IF(G126="","",TODAY()-G126)</f>
         <v/>
       </c>
-      <c r="I126" s="5" t="n"/>
-      <c r="J126" s="6" t="n"/>
-      <c r="K126" s="5" t="n"/>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L126" s="6" t="n"/>
-      <c r="M126" s="5" t="n"/>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N126" s="6" t="n"/>
-      <c r="O126" s="5" t="n"/>
+      <c r="O126" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P126" s="6" t="n"/>
-      <c r="Q126" s="5" t="n"/>
-      <c r="R126" s="5" t="n"/>
+      <c r="Q126" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R126" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n"/>
-      <c r="B127" s="5" t="n"/>
-      <c r="C127" s="5" t="n"/>
-      <c r="D127" s="5" t="n"/>
-      <c r="E127" s="5" t="n"/>
-      <c r="F127" s="5" t="n"/>
-      <c r="G127" s="6" t="n"/>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Vidur Gumber</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>vidur.gumber@valuehubit.com</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vidur-gumber-225219189</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H127" s="5">
         <f>IF(G127="","",TODAY()-G127)</f>
         <v/>
       </c>
-      <c r="I127" s="5" t="n"/>
-      <c r="J127" s="6" t="n"/>
-      <c r="K127" s="5" t="n"/>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L127" s="6" t="n"/>
-      <c r="M127" s="5" t="n"/>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N127" s="6" t="n"/>
-      <c r="O127" s="5" t="n"/>
+      <c r="O127" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P127" s="6" t="n"/>
-      <c r="Q127" s="5" t="n"/>
-      <c r="R127" s="5" t="n"/>
+      <c r="Q127" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R127" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n"/>
-      <c r="B128" s="5" t="n"/>
-      <c r="C128" s="5" t="n"/>
-      <c r="D128" s="5" t="n"/>
-      <c r="E128" s="5" t="n"/>
-      <c r="F128" s="5" t="n"/>
-      <c r="G128" s="6" t="n"/>
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Abbas Ratlamwala</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>abbas.ratlamwala@swansol.com</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/abbas-ratlamwala-973a6b20a</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H128" s="5">
         <f>IF(G128="","",TODAY()-G128)</f>
         <v/>
       </c>
-      <c r="I128" s="5" t="n"/>
-      <c r="J128" s="6" t="n"/>
-      <c r="K128" s="5" t="n"/>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L128" s="6" t="n"/>
-      <c r="M128" s="5" t="n"/>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N128" s="6" t="n"/>
-      <c r="O128" s="5" t="n"/>
+      <c r="O128" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P128" s="6" t="n"/>
-      <c r="Q128" s="5" t="n"/>
-      <c r="R128" s="5" t="n"/>
+      <c r="Q128" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R128" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n"/>
-      <c r="B129" s="5" t="n"/>
-      <c r="C129" s="5" t="n"/>
-      <c r="D129" s="5" t="n"/>
-      <c r="E129" s="5" t="n"/>
-      <c r="F129" s="5" t="n"/>
-      <c r="G129" s="6" t="n"/>
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Ishieka Jain</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>ishieka@veefin.com</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ishiekajain</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H129" s="5">
         <f>IF(G129="","",TODAY()-G129)</f>
         <v/>
       </c>
-      <c r="I129" s="5" t="n"/>
-      <c r="J129" s="6" t="n"/>
-      <c r="K129" s="5" t="n"/>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L129" s="6" t="n"/>
-      <c r="M129" s="5" t="n"/>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N129" s="6" t="n"/>
-      <c r="O129" s="5" t="n"/>
+      <c r="O129" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P129" s="6" t="n"/>
-      <c r="Q129" s="5" t="n"/>
-      <c r="R129" s="5" t="n"/>
+      <c r="Q129" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R129" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n"/>
-      <c r="B130" s="5" t="n"/>
-      <c r="C130" s="5" t="n"/>
-      <c r="D130" s="5" t="n"/>
-      <c r="E130" s="5" t="n"/>
-      <c r="F130" s="5" t="n"/>
-      <c r="G130" s="6" t="n"/>
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Ajithkumar Shanmugam</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>ajithkumar.s@thinkinnovsolution.com</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ajithkumar-shanmugam-592bb7153</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H130" s="5">
         <f>IF(G130="","",TODAY()-G130)</f>
         <v/>
       </c>
-      <c r="I130" s="5" t="n"/>
-      <c r="J130" s="6" t="n"/>
-      <c r="K130" s="5" t="n"/>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L130" s="6" t="n"/>
-      <c r="M130" s="5" t="n"/>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N130" s="6" t="n"/>
-      <c r="O130" s="5" t="n"/>
+      <c r="O130" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P130" s="6" t="n"/>
-      <c r="Q130" s="5" t="n"/>
-      <c r="R130" s="5" t="n"/>
+      <c r="Q130" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R130" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n"/>
-      <c r="B131" s="5" t="n"/>
-      <c r="C131" s="5" t="n"/>
-      <c r="D131" s="5" t="n"/>
-      <c r="E131" s="5" t="n"/>
-      <c r="F131" s="5" t="n"/>
-      <c r="G131" s="6" t="n"/>
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Garima Singh</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>garima.singh@execo.com</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/garimasingh08</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H131" s="5">
         <f>IF(G131="","",TODAY()-G131)</f>
         <v/>
       </c>
-      <c r="I131" s="5" t="n"/>
-      <c r="J131" s="6" t="n"/>
-      <c r="K131" s="5" t="n"/>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L131" s="6" t="n"/>
-      <c r="M131" s="5" t="n"/>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N131" s="6" t="n"/>
-      <c r="O131" s="5" t="n"/>
+      <c r="O131" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P131" s="6" t="n"/>
-      <c r="Q131" s="5" t="n"/>
-      <c r="R131" s="5" t="n"/>
+      <c r="Q131" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R131" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n"/>
-      <c r="B132" s="5" t="n"/>
-      <c r="C132" s="5" t="n"/>
-      <c r="D132" s="5" t="n"/>
-      <c r="E132" s="5" t="n"/>
-      <c r="F132" s="5" t="n"/>
-      <c r="G132" s="6" t="n"/>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Vaibhav Gopale</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>vaibhav.gopale@autoplant.in</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vaibhav-gopale-a428b3121</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H132" s="5">
         <f>IF(G132="","",TODAY()-G132)</f>
         <v/>
       </c>
-      <c r="I132" s="5" t="n"/>
-      <c r="J132" s="6" t="n"/>
-      <c r="K132" s="5" t="n"/>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L132" s="6" t="n"/>
-      <c r="M132" s="5" t="n"/>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N132" s="6" t="n"/>
-      <c r="O132" s="5" t="n"/>
+      <c r="O132" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P132" s="6" t="n"/>
-      <c r="Q132" s="5" t="n"/>
-      <c r="R132" s="5" t="n"/>
+      <c r="Q132" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R132" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n"/>
-      <c r="B133" s="5" t="n"/>
-      <c r="C133" s="5" t="n"/>
-      <c r="D133" s="5" t="n"/>
-      <c r="E133" s="5" t="n"/>
-      <c r="F133" s="5" t="n"/>
-      <c r="G133" s="6" t="n"/>
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Sagar Kirale</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>sagar.k@ioneitsolutions.com</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sagar-kirale-4a0728187</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H133" s="5">
         <f>IF(G133="","",TODAY()-G133)</f>
         <v/>
       </c>
-      <c r="I133" s="5" t="n"/>
-      <c r="J133" s="6" t="n"/>
-      <c r="K133" s="5" t="n"/>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L133" s="6" t="n"/>
-      <c r="M133" s="5" t="n"/>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N133" s="6" t="n"/>
-      <c r="O133" s="5" t="n"/>
+      <c r="O133" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P133" s="6" t="n"/>
-      <c r="Q133" s="5" t="n"/>
-      <c r="R133" s="5" t="n"/>
+      <c r="Q133" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R133" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n"/>
-      <c r="B134" s="5" t="n"/>
-      <c r="C134" s="5" t="n"/>
-      <c r="D134" s="5" t="n"/>
-      <c r="E134" s="5" t="n"/>
-      <c r="F134" s="5" t="n"/>
-      <c r="G134" s="6" t="n"/>
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Shantanu Shivarkar</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>shantanu.shivarkar@prospecta.com</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shantanu-shivarkar</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H134" s="5">
         <f>IF(G134="","",TODAY()-G134)</f>
         <v/>
       </c>
-      <c r="I134" s="5" t="n"/>
-      <c r="J134" s="6" t="n"/>
-      <c r="K134" s="5" t="n"/>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L134" s="6" t="n"/>
-      <c r="M134" s="5" t="n"/>
+      <c r="M134" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N134" s="6" t="n"/>
-      <c r="O134" s="5" t="n"/>
+      <c r="O134" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P134" s="6" t="n"/>
-      <c r="Q134" s="5" t="n"/>
-      <c r="R134" s="5" t="n"/>
+      <c r="Q134" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R134" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n"/>
-      <c r="B135" s="5" t="n"/>
-      <c r="C135" s="5" t="n"/>
-      <c r="D135" s="5" t="n"/>
-      <c r="E135" s="5" t="n"/>
-      <c r="F135" s="5" t="n"/>
-      <c r="G135" s="6" t="n"/>
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Varun Purwar</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>varun.purwar@cyfuture.com</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/varun-purwar-39a384247</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H135" s="5">
         <f>IF(G135="","",TODAY()-G135)</f>
         <v/>
       </c>
-      <c r="I135" s="5" t="n"/>
-      <c r="J135" s="6" t="n"/>
-      <c r="K135" s="5" t="n"/>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L135" s="6" t="n"/>
-      <c r="M135" s="5" t="n"/>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N135" s="6" t="n"/>
-      <c r="O135" s="5" t="n"/>
+      <c r="O135" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P135" s="6" t="n"/>
-      <c r="Q135" s="5" t="n"/>
-      <c r="R135" s="5" t="n"/>
+      <c r="Q135" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R135" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n"/>
-      <c r="B136" s="5" t="n"/>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="5" t="n"/>
-      <c r="E136" s="5" t="n"/>
-      <c r="F136" s="5" t="n"/>
-      <c r="G136" s="6" t="n"/>
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Hardique Pattnaik</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>hardique.pattnaik@genpact.com</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/hardique-abhinandan-pattnaik-a13aa1207</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H136" s="5">
         <f>IF(G136="","",TODAY()-G136)</f>
         <v/>
       </c>
-      <c r="I136" s="5" t="n"/>
-      <c r="J136" s="6" t="n"/>
-      <c r="K136" s="5" t="n"/>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L136" s="6" t="n"/>
-      <c r="M136" s="5" t="n"/>
+      <c r="M136" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N136" s="6" t="n"/>
-      <c r="O136" s="5" t="n"/>
+      <c r="O136" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P136" s="6" t="n"/>
-      <c r="Q136" s="5" t="n"/>
-      <c r="R136" s="5" t="n"/>
+      <c r="Q136" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R136" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n"/>
-      <c r="B137" s="5" t="n"/>
-      <c r="C137" s="5" t="n"/>
-      <c r="D137" s="5" t="n"/>
-      <c r="E137" s="5" t="n"/>
-      <c r="F137" s="5" t="n"/>
-      <c r="G137" s="6" t="n"/>
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Anyora Maheshwaree</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>anyora.maheshwaree@capgemini.com</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/anyora-maheshwaree-4765881b6</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H137" s="5">
         <f>IF(G137="","",TODAY()-G137)</f>
         <v/>
       </c>
-      <c r="I137" s="5" t="n"/>
-      <c r="J137" s="6" t="n"/>
-      <c r="K137" s="5" t="n"/>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L137" s="6" t="n"/>
-      <c r="M137" s="5" t="n"/>
+      <c r="M137" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N137" s="6" t="n"/>
-      <c r="O137" s="5" t="n"/>
+      <c r="O137" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P137" s="6" t="n"/>
-      <c r="Q137" s="5" t="n"/>
-      <c r="R137" s="5" t="n"/>
+      <c r="Q137" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R137" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n"/>
-      <c r="B138" s="5" t="n"/>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="5" t="n"/>
-      <c r="E138" s="5" t="n"/>
-      <c r="F138" s="5" t="n"/>
-      <c r="G138" s="6" t="n"/>
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Divyang Tripathi</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>divyang.tripathi@ltts.com</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/divyang-tripathi-1b7299170</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H138" s="5">
         <f>IF(G138="","",TODAY()-G138)</f>
         <v/>
       </c>
-      <c r="I138" s="5" t="n"/>
-      <c r="J138" s="6" t="n"/>
-      <c r="K138" s="5" t="n"/>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L138" s="6" t="n"/>
-      <c r="M138" s="5" t="n"/>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N138" s="6" t="n"/>
-      <c r="O138" s="5" t="n"/>
+      <c r="O138" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P138" s="6" t="n"/>
-      <c r="Q138" s="5" t="n"/>
-      <c r="R138" s="5" t="n"/>
+      <c r="Q138" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R138" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n"/>
-      <c r="B139" s="5" t="n"/>
-      <c r="C139" s="5" t="n"/>
-      <c r="D139" s="5" t="n"/>
-      <c r="E139" s="5" t="n"/>
-      <c r="F139" s="5" t="n"/>
-      <c r="G139" s="6" t="n"/>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Jaineel Patel</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>jaineel.patel@genzeon.com</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jaineel-patel</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H139" s="5">
         <f>IF(G139="","",TODAY()-G139)</f>
         <v/>
       </c>
-      <c r="I139" s="5" t="n"/>
-      <c r="J139" s="6" t="n"/>
-      <c r="K139" s="5" t="n"/>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L139" s="6" t="n"/>
-      <c r="M139" s="5" t="n"/>
+      <c r="M139" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N139" s="6" t="n"/>
-      <c r="O139" s="5" t="n"/>
+      <c r="O139" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P139" s="6" t="n"/>
-      <c r="Q139" s="5" t="n"/>
-      <c r="R139" s="5" t="n"/>
+      <c r="Q139" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R139" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n"/>
-      <c r="B140" s="5" t="n"/>
-      <c r="C140" s="5" t="n"/>
-      <c r="D140" s="5" t="n"/>
-      <c r="E140" s="5" t="n"/>
-      <c r="F140" s="5" t="n"/>
-      <c r="G140" s="6" t="n"/>
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Ruchita Kolla</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>kolla.ruchita@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ruchita-kolla</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H140" s="5">
         <f>IF(G140="","",TODAY()-G140)</f>
         <v/>
       </c>
-      <c r="I140" s="5" t="n"/>
-      <c r="J140" s="6" t="n"/>
-      <c r="K140" s="5" t="n"/>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L140" s="6" t="n"/>
-      <c r="M140" s="5" t="n"/>
+      <c r="M140" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N140" s="6" t="n"/>
-      <c r="O140" s="5" t="n"/>
+      <c r="O140" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P140" s="6" t="n"/>
-      <c r="Q140" s="5" t="n"/>
-      <c r="R140" s="5" t="n"/>
+      <c r="Q140" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R140" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="n"/>
-      <c r="B141" s="5" t="n"/>
-      <c r="C141" s="5" t="n"/>
-      <c r="D141" s="5" t="n"/>
-      <c r="E141" s="5" t="n"/>
-      <c r="F141" s="5" t="n"/>
-      <c r="G141" s="6" t="n"/>
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Amey Dalvi</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>amey.dalvi@teamcomputers.com</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/amey-dalvi-07504b131</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H141" s="5">
         <f>IF(G141="","",TODAY()-G141)</f>
         <v/>
       </c>
-      <c r="I141" s="5" t="n"/>
-      <c r="J141" s="6" t="n"/>
-      <c r="K141" s="5" t="n"/>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L141" s="6" t="n"/>
-      <c r="M141" s="5" t="n"/>
+      <c r="M141" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N141" s="6" t="n"/>
-      <c r="O141" s="5" t="n"/>
+      <c r="O141" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P141" s="6" t="n"/>
-      <c r="Q141" s="5" t="n"/>
-      <c r="R141" s="5" t="n"/>
+      <c r="Q141" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R141" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n"/>
-      <c r="B142" s="5" t="n"/>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="5" t="n"/>
-      <c r="E142" s="5" t="n"/>
-      <c r="F142" s="5" t="n"/>
-      <c r="G142" s="6" t="n"/>
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Dushyant Shah</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>dushyant.shah@appstrail.com</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dushyantshahpm</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H142" s="5">
         <f>IF(G142="","",TODAY()-G142)</f>
         <v/>
       </c>
-      <c r="I142" s="5" t="n"/>
-      <c r="J142" s="6" t="n"/>
-      <c r="K142" s="5" t="n"/>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L142" s="6" t="n"/>
-      <c r="M142" s="5" t="n"/>
+      <c r="M142" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N142" s="6" t="n"/>
-      <c r="O142" s="5" t="n"/>
+      <c r="O142" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P142" s="6" t="n"/>
-      <c r="Q142" s="5" t="n"/>
-      <c r="R142" s="5" t="n"/>
+      <c r="Q142" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R142" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n"/>
-      <c r="B143" s="5" t="n"/>
-      <c r="C143" s="5" t="n"/>
-      <c r="D143" s="5" t="n"/>
-      <c r="E143" s="5" t="n"/>
-      <c r="F143" s="5" t="n"/>
-      <c r="G143" s="6" t="n"/>
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Pranshur Dubey</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>pranshur.d@qbotica.com</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/pranshurdubey</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H143" s="5">
         <f>IF(G143="","",TODAY()-G143)</f>
         <v/>
       </c>
-      <c r="I143" s="5" t="n"/>
-      <c r="J143" s="6" t="n"/>
-      <c r="K143" s="5" t="n"/>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K143" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L143" s="6" t="n"/>
-      <c r="M143" s="5" t="n"/>
+      <c r="M143" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N143" s="6" t="n"/>
-      <c r="O143" s="5" t="n"/>
+      <c r="O143" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P143" s="6" t="n"/>
-      <c r="Q143" s="5" t="n"/>
-      <c r="R143" s="5" t="n"/>
+      <c r="Q143" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R143" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n"/>
-      <c r="B144" s="5" t="n"/>
-      <c r="C144" s="5" t="n"/>
-      <c r="D144" s="5" t="n"/>
-      <c r="E144" s="5" t="n"/>
-      <c r="F144" s="5" t="n"/>
-      <c r="G144" s="6" t="n"/>
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Kamya Batra</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>kbatra@eworkplaceapps.com</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/kamya-batra-3962ba220</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H144" s="5">
         <f>IF(G144="","",TODAY()-G144)</f>
         <v/>
       </c>
-      <c r="I144" s="5" t="n"/>
-      <c r="J144" s="6" t="n"/>
-      <c r="K144" s="5" t="n"/>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L144" s="6" t="n"/>
-      <c r="M144" s="5" t="n"/>
+      <c r="M144" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N144" s="6" t="n"/>
-      <c r="O144" s="5" t="n"/>
+      <c r="O144" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P144" s="6" t="n"/>
-      <c r="Q144" s="5" t="n"/>
-      <c r="R144" s="5" t="n"/>
+      <c r="Q144" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R144" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n"/>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="5" t="n"/>
-      <c r="E145" s="5" t="n"/>
-      <c r="F145" s="5" t="n"/>
-      <c r="G145" s="6" t="n"/>
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Shantanu Kulkarni</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>shantanu.k@autoplant.in</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shantanu-kulkarni-53506325</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H145" s="5">
         <f>IF(G145="","",TODAY()-G145)</f>
         <v/>
       </c>
-      <c r="I145" s="5" t="n"/>
-      <c r="J145" s="6" t="n"/>
-      <c r="K145" s="5" t="n"/>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L145" s="6" t="n"/>
-      <c r="M145" s="5" t="n"/>
+      <c r="M145" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N145" s="6" t="n"/>
-      <c r="O145" s="5" t="n"/>
+      <c r="O145" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P145" s="6" t="n"/>
-      <c r="Q145" s="5" t="n"/>
-      <c r="R145" s="5" t="n"/>
+      <c r="Q145" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R145" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n"/>
-      <c r="B146" s="5" t="n"/>
-      <c r="C146" s="5" t="n"/>
-      <c r="D146" s="5" t="n"/>
-      <c r="E146" s="5" t="n"/>
-      <c r="F146" s="5" t="n"/>
-      <c r="G146" s="6" t="n"/>
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Priya Panchal</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>priya.panchal@mewurk.com</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/priya-panchal-8a1947292</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H146" s="5">
         <f>IF(G146="","",TODAY()-G146)</f>
         <v/>
       </c>
-      <c r="I146" s="5" t="n"/>
-      <c r="J146" s="6" t="n"/>
-      <c r="K146" s="5" t="n"/>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L146" s="6" t="n"/>
-      <c r="M146" s="5" t="n"/>
+      <c r="M146" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N146" s="6" t="n"/>
-      <c r="O146" s="5" t="n"/>
+      <c r="O146" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P146" s="6" t="n"/>
-      <c r="Q146" s="5" t="n"/>
-      <c r="R146" s="5" t="n"/>
+      <c r="Q146" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R146" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n"/>
-      <c r="B147" s="5" t="n"/>
-      <c r="C147" s="5" t="n"/>
-      <c r="D147" s="5" t="n"/>
-      <c r="E147" s="5" t="n"/>
-      <c r="F147" s="5" t="n"/>
-      <c r="G147" s="6" t="n"/>
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Mohammad Shoaib</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>mohammad.shoaib@sotiotech.com</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/mohammad-shoaib-408b45245</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H147" s="5">
         <f>IF(G147="","",TODAY()-G147)</f>
         <v/>
       </c>
-      <c r="I147" s="5" t="n"/>
-      <c r="J147" s="6" t="n"/>
-      <c r="K147" s="5" t="n"/>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L147" s="6" t="n"/>
-      <c r="M147" s="5" t="n"/>
+      <c r="M147" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N147" s="6" t="n"/>
-      <c r="O147" s="5" t="n"/>
+      <c r="O147" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P147" s="6" t="n"/>
-      <c r="Q147" s="5" t="n"/>
-      <c r="R147" s="5" t="n"/>
+      <c r="Q147" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R147" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n"/>
-      <c r="B148" s="5" t="n"/>
-      <c r="C148" s="5" t="n"/>
-      <c r="D148" s="5" t="n"/>
-      <c r="E148" s="5" t="n"/>
-      <c r="F148" s="5" t="n"/>
-      <c r="G148" s="6" t="n"/>
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Shubham Tyagi</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>shubham.tyagi@wipro.com</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/imshubhamtyagi</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H148" s="5">
         <f>IF(G148="","",TODAY()-G148)</f>
         <v/>
       </c>
-      <c r="I148" s="5" t="n"/>
-      <c r="J148" s="6" t="n"/>
-      <c r="K148" s="5" t="n"/>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L148" s="6" t="n"/>
-      <c r="M148" s="5" t="n"/>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N148" s="6" t="n"/>
-      <c r="O148" s="5" t="n"/>
+      <c r="O148" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P148" s="6" t="n"/>
-      <c r="Q148" s="5" t="n"/>
-      <c r="R148" s="5" t="n"/>
+      <c r="Q148" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R148" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n"/>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="5" t="n"/>
-      <c r="D149" s="5" t="n"/>
-      <c r="E149" s="5" t="n"/>
-      <c r="F149" s="5" t="n"/>
-      <c r="G149" s="6" t="n"/>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Madhukar Km</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>mkm@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/madhukar-km</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H149" s="5">
         <f>IF(G149="","",TODAY()-G149)</f>
         <v/>
       </c>
-      <c r="I149" s="5" t="n"/>
-      <c r="J149" s="6" t="n"/>
-      <c r="K149" s="5" t="n"/>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L149" s="6" t="n"/>
-      <c r="M149" s="5" t="n"/>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N149" s="6" t="n"/>
-      <c r="O149" s="5" t="n"/>
+      <c r="O149" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P149" s="6" t="n"/>
-      <c r="Q149" s="5" t="n"/>
-      <c r="R149" s="5" t="n"/>
+      <c r="Q149" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R149" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="5" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="n"/>
-      <c r="E150" s="5" t="n"/>
-      <c r="F150" s="5" t="n"/>
-      <c r="G150" s="6" t="n"/>
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Kundan Pathak</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>kundan.pathak@cognizant.com</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/kundan-pathak</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H150" s="5">
         <f>IF(G150="","",TODAY()-G150)</f>
         <v/>
       </c>
-      <c r="I150" s="5" t="n"/>
-      <c r="J150" s="6" t="n"/>
-      <c r="K150" s="5" t="n"/>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L150" s="6" t="n"/>
-      <c r="M150" s="5" t="n"/>
+      <c r="M150" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N150" s="6" t="n"/>
-      <c r="O150" s="5" t="n"/>
+      <c r="O150" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P150" s="6" t="n"/>
-      <c r="Q150" s="5" t="n"/>
-      <c r="R150" s="5" t="n"/>
+      <c r="Q150" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R150" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n"/>
-      <c r="B151" s="5" t="n"/>
-      <c r="C151" s="5" t="n"/>
-      <c r="D151" s="5" t="n"/>
-      <c r="E151" s="5" t="n"/>
-      <c r="F151" s="5" t="n"/>
-      <c r="G151" s="6" t="n"/>
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Pratul Roy</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>pratul.roy@nagarro.com</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/pratul-roy-54869415a</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H151" s="5">
         <f>IF(G151="","",TODAY()-G151)</f>
         <v/>
       </c>
-      <c r="I151" s="5" t="n"/>
-      <c r="J151" s="6" t="n"/>
-      <c r="K151" s="5" t="n"/>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L151" s="6" t="n"/>
-      <c r="M151" s="5" t="n"/>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N151" s="6" t="n"/>
-      <c r="O151" s="5" t="n"/>
+      <c r="O151" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P151" s="6" t="n"/>
-      <c r="Q151" s="5" t="n"/>
-      <c r="R151" s="5" t="n"/>
+      <c r="Q151" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R151" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="n"/>
-      <c r="B152" s="5" t="n"/>
-      <c r="C152" s="5" t="n"/>
-      <c r="D152" s="5" t="n"/>
-      <c r="E152" s="5" t="n"/>
-      <c r="F152" s="5" t="n"/>
-      <c r="G152" s="6" t="n"/>
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Ayush Srivastava</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>ayush.srivastava@essindia.com</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ayush-srivastava-914136229</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H152" s="5">
         <f>IF(G152="","",TODAY()-G152)</f>
         <v/>
       </c>
-      <c r="I152" s="5" t="n"/>
-      <c r="J152" s="6" t="n"/>
-      <c r="K152" s="5" t="n"/>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L152" s="6" t="n"/>
-      <c r="M152" s="5" t="n"/>
+      <c r="M152" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N152" s="6" t="n"/>
-      <c r="O152" s="5" t="n"/>
+      <c r="O152" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P152" s="6" t="n"/>
-      <c r="Q152" s="5" t="n"/>
-      <c r="R152" s="5" t="n"/>
+      <c r="Q152" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R152" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n"/>
-      <c r="B153" s="5" t="n"/>
-      <c r="C153" s="5" t="n"/>
-      <c r="D153" s="5" t="n"/>
-      <c r="E153" s="5" t="n"/>
-      <c r="F153" s="5" t="n"/>
-      <c r="G153" s="6" t="n"/>
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Shubhangi Srivastava</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>shubhangis@vastedge.com</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shubhangi-srivastava-b3b0331b5</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H153" s="5">
         <f>IF(G153="","",TODAY()-G153)</f>
         <v/>
       </c>
-      <c r="I153" s="5" t="n"/>
-      <c r="J153" s="6" t="n"/>
-      <c r="K153" s="5" t="n"/>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L153" s="6" t="n"/>
-      <c r="M153" s="5" t="n"/>
+      <c r="M153" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N153" s="6" t="n"/>
-      <c r="O153" s="5" t="n"/>
+      <c r="O153" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P153" s="6" t="n"/>
-      <c r="Q153" s="5" t="n"/>
-      <c r="R153" s="5" t="n"/>
+      <c r="Q153" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R153" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n"/>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="5" t="n"/>
-      <c r="E154" s="5" t="n"/>
-      <c r="F154" s="5" t="n"/>
-      <c r="G154" s="6" t="n"/>
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Anwesha Banerjee</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>anwesha.banerjee@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/anwesha-banerjee-baa503205</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H154" s="5">
         <f>IF(G154="","",TODAY()-G154)</f>
         <v/>
       </c>
-      <c r="I154" s="5" t="n"/>
-      <c r="J154" s="6" t="n"/>
-      <c r="K154" s="5" t="n"/>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L154" s="6" t="n"/>
-      <c r="M154" s="5" t="n"/>
+      <c r="M154" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N154" s="6" t="n"/>
-      <c r="O154" s="5" t="n"/>
+      <c r="O154" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P154" s="6" t="n"/>
-      <c r="Q154" s="5" t="n"/>
-      <c r="R154" s="5" t="n"/>
+      <c r="Q154" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R154" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n"/>
-      <c r="B155" s="5" t="n"/>
-      <c r="C155" s="5" t="n"/>
-      <c r="D155" s="5" t="n"/>
-      <c r="E155" s="5" t="n"/>
-      <c r="F155" s="5" t="n"/>
-      <c r="G155" s="6" t="n"/>
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Vaishnavi Kumbhar</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>vaishnavi.kumbhar@accenture.com</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vaishnavi-kumbhar-7306b2250</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H155" s="5">
         <f>IF(G155="","",TODAY()-G155)</f>
         <v/>
       </c>
-      <c r="I155" s="5" t="n"/>
-      <c r="J155" s="6" t="n"/>
-      <c r="K155" s="5" t="n"/>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L155" s="6" t="n"/>
-      <c r="M155" s="5" t="n"/>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N155" s="6" t="n"/>
-      <c r="O155" s="5" t="n"/>
+      <c r="O155" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P155" s="6" t="n"/>
-      <c r="Q155" s="5" t="n"/>
-      <c r="R155" s="5" t="n"/>
+      <c r="Q155" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R155" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n"/>
-      <c r="B156" s="5" t="n"/>
-      <c r="C156" s="5" t="n"/>
-      <c r="D156" s="5" t="n"/>
-      <c r="E156" s="5" t="n"/>
-      <c r="F156" s="5" t="n"/>
-      <c r="G156" s="6" t="n"/>
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Parv Bansal</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>parv.bansal@wipro.com</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/bansal-parv</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H156" s="5">
         <f>IF(G156="","",TODAY()-G156)</f>
         <v/>
       </c>
-      <c r="I156" s="5" t="n"/>
-      <c r="J156" s="6" t="n"/>
-      <c r="K156" s="5" t="n"/>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L156" s="6" t="n"/>
-      <c r="M156" s="5" t="n"/>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N156" s="6" t="n"/>
-      <c r="O156" s="5" t="n"/>
+      <c r="O156" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P156" s="6" t="n"/>
-      <c r="Q156" s="5" t="n"/>
-      <c r="R156" s="5" t="n"/>
+      <c r="Q156" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="R156" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="n"/>
-      <c r="B157" s="5" t="n"/>
-      <c r="C157" s="5" t="n"/>
-      <c r="D157" s="5" t="n"/>
-      <c r="E157" s="5" t="n"/>
-      <c r="F157" s="5" t="n"/>
-      <c r="G157" s="6" t="n"/>
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Jaden Toh</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>jaden.toh@alpha-sense.com</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jadentoh</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H157" s="5">
         <f>IF(G157="","",TODAY()-G157)</f>
         <v/>
       </c>
-      <c r="I157" s="5" t="n"/>
-      <c r="J157" s="6" t="n"/>
-      <c r="K157" s="5" t="n"/>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L157" s="6" t="n"/>
-      <c r="M157" s="5" t="n"/>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N157" s="6" t="n"/>
-      <c r="O157" s="5" t="n"/>
+      <c r="O157" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P157" s="6" t="n"/>
-      <c r="Q157" s="5" t="n"/>
-      <c r="R157" s="5" t="n"/>
+      <c r="Q157" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="R157" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n"/>
-      <c r="B158" s="5" t="n"/>
-      <c r="C158" s="5" t="n"/>
-      <c r="D158" s="5" t="n"/>
-      <c r="E158" s="5" t="n"/>
-      <c r="F158" s="5" t="n"/>
-      <c r="G158" s="6" t="n"/>
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>Claire Kao</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>clairekao@bigobject.io</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/claire-ting-wei-kao-b74b1110b</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H158" s="5">
         <f>IF(G158="","",TODAY()-G158)</f>
         <v/>
       </c>
-      <c r="I158" s="5" t="n"/>
-      <c r="J158" s="6" t="n"/>
-      <c r="K158" s="5" t="n"/>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L158" s="6" t="n"/>
-      <c r="M158" s="5" t="n"/>
+      <c r="M158" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N158" s="6" t="n"/>
-      <c r="O158" s="5" t="n"/>
+      <c r="O158" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P158" s="6" t="n"/>
-      <c r="Q158" s="5" t="n"/>
-      <c r="R158" s="5" t="n"/>
+      <c r="Q158" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="R158" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="n"/>
-      <c r="B159" s="5" t="n"/>
-      <c r="C159" s="5" t="n"/>
-      <c r="D159" s="5" t="n"/>
-      <c r="E159" s="5" t="n"/>
-      <c r="F159" s="5" t="n"/>
-      <c r="G159" s="6" t="n"/>
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Gracia Kwantalalu</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>gracia.kwantalalu@avepoint.com</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/gracia-yk</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H159" s="5">
         <f>IF(G159="","",TODAY()-G159)</f>
         <v/>
       </c>
-      <c r="I159" s="5" t="n"/>
-      <c r="J159" s="6" t="n"/>
-      <c r="K159" s="5" t="n"/>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L159" s="6" t="n"/>
-      <c r="M159" s="5" t="n"/>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N159" s="6" t="n"/>
-      <c r="O159" s="5" t="n"/>
+      <c r="O159" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P159" s="6" t="n"/>
-      <c r="Q159" s="5" t="n"/>
-      <c r="R159" s="5" t="n"/>
+      <c r="Q159" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n"/>
-      <c r="B160" s="5" t="n"/>
-      <c r="C160" s="5" t="n"/>
-      <c r="D160" s="5" t="n"/>
-      <c r="E160" s="5" t="n"/>
-      <c r="F160" s="5" t="n"/>
-      <c r="G160" s="6" t="n"/>
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Wenxi Liu</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>wenxi.liu@quanthouse.com</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/wenxi-liu</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H160" s="5">
         <f>IF(G160="","",TODAY()-G160)</f>
         <v/>
       </c>
-      <c r="I160" s="5" t="n"/>
-      <c r="J160" s="6" t="n"/>
-      <c r="K160" s="5" t="n"/>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L160" s="6" t="n"/>
-      <c r="M160" s="5" t="n"/>
+      <c r="M160" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N160" s="6" t="n"/>
-      <c r="O160" s="5" t="n"/>
+      <c r="O160" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P160" s="6" t="n"/>
-      <c r="Q160" s="5" t="n"/>
-      <c r="R160" s="5" t="n"/>
+      <c r="Q160" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="R160" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n"/>
-      <c r="B161" s="5" t="n"/>
-      <c r="C161" s="5" t="n"/>
-      <c r="D161" s="5" t="n"/>
-      <c r="E161" s="5" t="n"/>
-      <c r="F161" s="5" t="n"/>
-      <c r="G161" s="6" t="n"/>
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Joshua Aw</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>joshuaaw@mtechpro.com</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/joshua-aw-0a9634234</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Sales &amp; Presales Career Progression</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Email 1 Sent</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="n">
+        <v>46280</v>
+      </c>
       <c r="H161" s="5">
         <f>IF(G161="","",TODAY()-G161)</f>
         <v/>
       </c>
-      <c r="I161" s="5" t="n"/>
-      <c r="J161" s="6" t="n"/>
-      <c r="K161" s="5" t="n"/>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>Send Follow-up 1</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K161" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L161" s="6" t="n"/>
-      <c r="M161" s="5" t="n"/>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="N161" s="6" t="n"/>
-      <c r="O161" s="5" t="n"/>
+      <c r="O161" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P161" s="6" t="n"/>
-      <c r="Q161" s="5" t="n"/>
-      <c r="R161" s="5" t="n"/>
+      <c r="Q161" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="R161" s="5" t="inlineStr">
+        <is>
+          <t>Manually sourced via Apollo web UI (user-uploaded file "Presales_SalesEngineer_Candidates_1.xlsx", not via manual_sourcing/ folder) — Segment A1 Presales, ad hoc processing on 2026-09-15 at user's request; secondary Presales Mock Interview mention included in Email 1.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -17143,703 +19743,2803 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n"/>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="5" t="n"/>
-      <c r="F115" s="5" t="n"/>
-      <c r="G115" s="5" t="n"/>
-      <c r="H115" s="5" t="n"/>
-      <c r="I115" s="5" t="n"/>
-      <c r="J115" s="6" t="n"/>
-      <c r="K115" s="5" t="n"/>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Yuvika Sharma</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>yuvika.sharma@tecnotree.com</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/yuvika-sharma-3370b6147</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Tecnotree Corporation</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L115" s="5" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n"/>
-      <c r="B116" s="5" t="n"/>
-      <c r="C116" s="5" t="n"/>
-      <c r="D116" s="5" t="n"/>
-      <c r="E116" s="5" t="n"/>
-      <c r="F116" s="5" t="n"/>
-      <c r="G116" s="5" t="n"/>
-      <c r="H116" s="5" t="n"/>
-      <c r="I116" s="5" t="n"/>
-      <c r="J116" s="6" t="n"/>
-      <c r="K116" s="5" t="n"/>
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Pratiksha Kulkarni</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>pratiksha.kulkarni@solytics-partners.com</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/pratiksha-kulkarni-615139148</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Solytics Partners</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L116" s="5" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n"/>
-      <c r="B117" s="5" t="n"/>
-      <c r="C117" s="5" t="n"/>
-      <c r="D117" s="5" t="n"/>
-      <c r="E117" s="5" t="n"/>
-      <c r="F117" s="5" t="n"/>
-      <c r="G117" s="5" t="n"/>
-      <c r="H117" s="5" t="n"/>
-      <c r="I117" s="5" t="n"/>
-      <c r="J117" s="6" t="n"/>
-      <c r="K117" s="5" t="n"/>
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Esha Gulati</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>esha.gulati@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/esha-gulati</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L117" s="5" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n"/>
-      <c r="B118" s="5" t="n"/>
-      <c r="C118" s="5" t="n"/>
-      <c r="D118" s="5" t="n"/>
-      <c r="E118" s="5" t="n"/>
-      <c r="F118" s="5" t="n"/>
-      <c r="G118" s="5" t="n"/>
-      <c r="H118" s="5" t="n"/>
-      <c r="I118" s="5" t="n"/>
-      <c r="J118" s="6" t="n"/>
-      <c r="K118" s="5" t="n"/>
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Sharvari Rao</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>sharvari.rao@ptrglobal.com</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sharvari-rao-711b6a1a2</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>PTR Global</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L118" s="5" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n"/>
-      <c r="B119" s="5" t="n"/>
-      <c r="C119" s="5" t="n"/>
-      <c r="D119" s="5" t="n"/>
-      <c r="E119" s="5" t="n"/>
-      <c r="F119" s="5" t="n"/>
-      <c r="G119" s="5" t="n"/>
-      <c r="H119" s="5" t="n"/>
-      <c r="I119" s="5" t="n"/>
-      <c r="J119" s="6" t="n"/>
-      <c r="K119" s="5" t="n"/>
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Bhushan Raut</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>bhushan.r@indictranstech.com</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/bhushanraut43</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Indictrans</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L119" s="5" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n"/>
-      <c r="B120" s="5" t="n"/>
-      <c r="C120" s="5" t="n"/>
-      <c r="D120" s="5" t="n"/>
-      <c r="E120" s="5" t="n"/>
-      <c r="F120" s="5" t="n"/>
-      <c r="G120" s="5" t="n"/>
-      <c r="H120" s="5" t="n"/>
-      <c r="I120" s="5" t="n"/>
-      <c r="J120" s="6" t="n"/>
-      <c r="K120" s="5" t="n"/>
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Ambarish Khound</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>ambarish.khound@metricstream.com</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ambarishkhound</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>MetricStream</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L120" s="5" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n"/>
-      <c r="B121" s="5" t="n"/>
-      <c r="C121" s="5" t="n"/>
-      <c r="D121" s="5" t="n"/>
-      <c r="E121" s="5" t="n"/>
-      <c r="F121" s="5" t="n"/>
-      <c r="G121" s="5" t="n"/>
-      <c r="H121" s="5" t="n"/>
-      <c r="I121" s="5" t="n"/>
-      <c r="J121" s="6" t="n"/>
-      <c r="K121" s="5" t="n"/>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Vikash Meena</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>vikash.meena@photon.com</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/iamvikash96</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Photon</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L121" s="5" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n"/>
-      <c r="B122" s="5" t="n"/>
-      <c r="C122" s="5" t="n"/>
-      <c r="D122" s="5" t="n"/>
-      <c r="E122" s="5" t="n"/>
-      <c r="F122" s="5" t="n"/>
-      <c r="G122" s="5" t="n"/>
-      <c r="H122" s="5" t="n"/>
-      <c r="I122" s="5" t="n"/>
-      <c r="J122" s="6" t="n"/>
-      <c r="K122" s="5" t="n"/>
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Himani Ahuja</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>himani.ahuja@solytics-partners.com</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/himani-ahuja-532a39233</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Solytics Partners</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L122" s="5" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n"/>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="5" t="n"/>
-      <c r="D123" s="5" t="n"/>
-      <c r="E123" s="5" t="n"/>
-      <c r="F123" s="5" t="n"/>
-      <c r="G123" s="5" t="n"/>
-      <c r="H123" s="5" t="n"/>
-      <c r="I123" s="5" t="n"/>
-      <c r="J123" s="6" t="n"/>
-      <c r="K123" s="5" t="n"/>
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Manav Juneja</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>manav.juneja@infojiniconsulting.com</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/manavjuneja84</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Infojini Inc</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L123" s="5" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n"/>
-      <c r="B124" s="5" t="n"/>
-      <c r="C124" s="5" t="n"/>
-      <c r="D124" s="5" t="n"/>
-      <c r="E124" s="5" t="n"/>
-      <c r="F124" s="5" t="n"/>
-      <c r="G124" s="5" t="n"/>
-      <c r="H124" s="5" t="n"/>
-      <c r="I124" s="5" t="n"/>
-      <c r="J124" s="6" t="n"/>
-      <c r="K124" s="5" t="n"/>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Krishna Kulkarni</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>kulkarnik@hcl.com</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/krishna-k9</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L124" s="5" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n"/>
-      <c r="B125" s="5" t="n"/>
-      <c r="C125" s="5" t="n"/>
-      <c r="D125" s="5" t="n"/>
-      <c r="E125" s="5" t="n"/>
-      <c r="F125" s="5" t="n"/>
-      <c r="G125" s="5" t="n"/>
-      <c r="H125" s="5" t="n"/>
-      <c r="I125" s="5" t="n"/>
-      <c r="J125" s="6" t="n"/>
-      <c r="K125" s="5" t="n"/>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Shivani Singh</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>shivani.singh@incitegravity.com</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shivani-singh2815</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Incite Gravity</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L125" s="5" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n"/>
-      <c r="B126" s="5" t="n"/>
-      <c r="C126" s="5" t="n"/>
-      <c r="D126" s="5" t="n"/>
-      <c r="E126" s="5" t="n"/>
-      <c r="F126" s="5" t="n"/>
-      <c r="G126" s="5" t="n"/>
-      <c r="H126" s="5" t="n"/>
-      <c r="I126" s="5" t="n"/>
-      <c r="J126" s="6" t="n"/>
-      <c r="K126" s="5" t="n"/>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Sumit Tyagi</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>sumit.tyagi3@wipro.com</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sumit-tyagi-7aa00562</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L126" s="5" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n"/>
-      <c r="B127" s="5" t="n"/>
-      <c r="C127" s="5" t="n"/>
-      <c r="D127" s="5" t="n"/>
-      <c r="E127" s="5" t="n"/>
-      <c r="F127" s="5" t="n"/>
-      <c r="G127" s="5" t="n"/>
-      <c r="H127" s="5" t="n"/>
-      <c r="I127" s="5" t="n"/>
-      <c r="J127" s="6" t="n"/>
-      <c r="K127" s="5" t="n"/>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Animesh Anand</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>animesha@maqsoftware.com</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/animesh-anand-mba</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>T-Systems ICT India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L127" s="5" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n"/>
-      <c r="B128" s="5" t="n"/>
-      <c r="C128" s="5" t="n"/>
-      <c r="D128" s="5" t="n"/>
-      <c r="E128" s="5" t="n"/>
-      <c r="F128" s="5" t="n"/>
-      <c r="G128" s="5" t="n"/>
-      <c r="H128" s="5" t="n"/>
-      <c r="I128" s="5" t="n"/>
-      <c r="J128" s="6" t="n"/>
-      <c r="K128" s="5" t="n"/>
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Himanshu Shende</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>himanshu.shende@wipro.com</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/himanshu-shende55555</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L128" s="5" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n"/>
-      <c r="B129" s="5" t="n"/>
-      <c r="C129" s="5" t="n"/>
-      <c r="D129" s="5" t="n"/>
-      <c r="E129" s="5" t="n"/>
-      <c r="F129" s="5" t="n"/>
-      <c r="G129" s="5" t="n"/>
-      <c r="H129" s="5" t="n"/>
-      <c r="I129" s="5" t="n"/>
-      <c r="J129" s="6" t="n"/>
-      <c r="K129" s="5" t="n"/>
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Akanksha Barnwal</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>akanksha.b@infosys.com</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/akanksha-barnwal-84b082114</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L129" s="5" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n"/>
-      <c r="B130" s="5" t="n"/>
-      <c r="C130" s="5" t="n"/>
-      <c r="D130" s="5" t="n"/>
-      <c r="E130" s="5" t="n"/>
-      <c r="F130" s="5" t="n"/>
-      <c r="G130" s="5" t="n"/>
-      <c r="H130" s="5" t="n"/>
-      <c r="I130" s="5" t="n"/>
-      <c r="J130" s="6" t="n"/>
-      <c r="K130" s="5" t="n"/>
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Vidur Gumber</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>vidur.gumber@valuehubit.com</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vidur-gumber-225219189</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Valuehub</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L130" s="5" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n"/>
-      <c r="B131" s="5" t="n"/>
-      <c r="C131" s="5" t="n"/>
-      <c r="D131" s="5" t="n"/>
-      <c r="E131" s="5" t="n"/>
-      <c r="F131" s="5" t="n"/>
-      <c r="G131" s="5" t="n"/>
-      <c r="H131" s="5" t="n"/>
-      <c r="I131" s="5" t="n"/>
-      <c r="J131" s="6" t="n"/>
-      <c r="K131" s="5" t="n"/>
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Abbas Ratlamwala</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>abbas.ratlamwala@swansol.com</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/abbas-ratlamwala-973a6b20a</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Swan Solutions &amp; Services Pvt Ltd.</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L131" s="5" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n"/>
-      <c r="B132" s="5" t="n"/>
-      <c r="C132" s="5" t="n"/>
-      <c r="D132" s="5" t="n"/>
-      <c r="E132" s="5" t="n"/>
-      <c r="F132" s="5" t="n"/>
-      <c r="G132" s="5" t="n"/>
-      <c r="H132" s="5" t="n"/>
-      <c r="I132" s="5" t="n"/>
-      <c r="J132" s="6" t="n"/>
-      <c r="K132" s="5" t="n"/>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Ishieka Jain</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>ishieka@veefin.com</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ishiekajain</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Veefin</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L132" s="5" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n"/>
-      <c r="B133" s="5" t="n"/>
-      <c r="C133" s="5" t="n"/>
-      <c r="D133" s="5" t="n"/>
-      <c r="E133" s="5" t="n"/>
-      <c r="F133" s="5" t="n"/>
-      <c r="G133" s="5" t="n"/>
-      <c r="H133" s="5" t="n"/>
-      <c r="I133" s="5" t="n"/>
-      <c r="J133" s="6" t="n"/>
-      <c r="K133" s="5" t="n"/>
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Ajithkumar Shanmugam</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>ajithkumar.s@thinkinnovsolution.com</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ajithkumar-shanmugam-592bb7153</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Thinkinnov Solution Technologies Private Limited</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L133" s="5" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n"/>
-      <c r="B134" s="5" t="n"/>
-      <c r="C134" s="5" t="n"/>
-      <c r="D134" s="5" t="n"/>
-      <c r="E134" s="5" t="n"/>
-      <c r="F134" s="5" t="n"/>
-      <c r="G134" s="5" t="n"/>
-      <c r="H134" s="5" t="n"/>
-      <c r="I134" s="5" t="n"/>
-      <c r="J134" s="6" t="n"/>
-      <c r="K134" s="5" t="n"/>
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Garima Singh</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>garima.singh@execo.com</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/garimasingh08</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Execo</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L134" s="5" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n"/>
-      <c r="B135" s="5" t="n"/>
-      <c r="C135" s="5" t="n"/>
-      <c r="D135" s="5" t="n"/>
-      <c r="E135" s="5" t="n"/>
-      <c r="F135" s="5" t="n"/>
-      <c r="G135" s="5" t="n"/>
-      <c r="H135" s="5" t="n"/>
-      <c r="I135" s="5" t="n"/>
-      <c r="J135" s="6" t="n"/>
-      <c r="K135" s="5" t="n"/>
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Vaibhav Gopale</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>vaibhav.gopale@autoplant.in</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vaibhav-gopale-a428b3121</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Autoplant System India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L135" s="5" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n"/>
-      <c r="B136" s="5" t="n"/>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="5" t="n"/>
-      <c r="E136" s="5" t="n"/>
-      <c r="F136" s="5" t="n"/>
-      <c r="G136" s="5" t="n"/>
-      <c r="H136" s="5" t="n"/>
-      <c r="I136" s="5" t="n"/>
-      <c r="J136" s="6" t="n"/>
-      <c r="K136" s="5" t="n"/>
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Sagar Kirale</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>sagar.k@ioneitsolutions.com</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sagar-kirale-4a0728187</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>iONE IT Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L136" s="5" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n"/>
-      <c r="B137" s="5" t="n"/>
-      <c r="C137" s="5" t="n"/>
-      <c r="D137" s="5" t="n"/>
-      <c r="E137" s="5" t="n"/>
-      <c r="F137" s="5" t="n"/>
-      <c r="G137" s="5" t="n"/>
-      <c r="H137" s="5" t="n"/>
-      <c r="I137" s="5" t="n"/>
-      <c r="J137" s="6" t="n"/>
-      <c r="K137" s="5" t="n"/>
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Shantanu Shivarkar</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>shantanu.shivarkar@prospecta.com</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shantanu-shivarkar</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Prospecta Software</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L137" s="5" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n"/>
-      <c r="B138" s="5" t="n"/>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="5" t="n"/>
-      <c r="E138" s="5" t="n"/>
-      <c r="F138" s="5" t="n"/>
-      <c r="G138" s="5" t="n"/>
-      <c r="H138" s="5" t="n"/>
-      <c r="I138" s="5" t="n"/>
-      <c r="J138" s="6" t="n"/>
-      <c r="K138" s="5" t="n"/>
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Varun Purwar</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>varun.purwar@cyfuture.com</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/varun-purwar-39a384247</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Cyfuture</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L138" s="5" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n"/>
-      <c r="B139" s="5" t="n"/>
-      <c r="C139" s="5" t="n"/>
-      <c r="D139" s="5" t="n"/>
-      <c r="E139" s="5" t="n"/>
-      <c r="F139" s="5" t="n"/>
-      <c r="G139" s="5" t="n"/>
-      <c r="H139" s="5" t="n"/>
-      <c r="I139" s="5" t="n"/>
-      <c r="J139" s="6" t="n"/>
-      <c r="K139" s="5" t="n"/>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Hardique Pattnaik</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>hardique.pattnaik@genpact.com</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/hardique-abhinandan-pattnaik-a13aa1207</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L139" s="5" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n"/>
-      <c r="B140" s="5" t="n"/>
-      <c r="C140" s="5" t="n"/>
-      <c r="D140" s="5" t="n"/>
-      <c r="E140" s="5" t="n"/>
-      <c r="F140" s="5" t="n"/>
-      <c r="G140" s="5" t="n"/>
-      <c r="H140" s="5" t="n"/>
-      <c r="I140" s="5" t="n"/>
-      <c r="J140" s="6" t="n"/>
-      <c r="K140" s="5" t="n"/>
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Anyora Maheshwaree</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>anyora.maheshwaree@capgemini.com</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/anyora-maheshwaree-4765881b6</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L140" s="5" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="n"/>
-      <c r="B141" s="5" t="n"/>
-      <c r="C141" s="5" t="n"/>
-      <c r="D141" s="5" t="n"/>
-      <c r="E141" s="5" t="n"/>
-      <c r="F141" s="5" t="n"/>
-      <c r="G141" s="5" t="n"/>
-      <c r="H141" s="5" t="n"/>
-      <c r="I141" s="5" t="n"/>
-      <c r="J141" s="6" t="n"/>
-      <c r="K141" s="5" t="n"/>
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Divyang Tripathi</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>divyang.tripathi@ltts.com</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/divyang-tripathi-1b7299170</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L141" s="5" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n"/>
-      <c r="B142" s="5" t="n"/>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="5" t="n"/>
-      <c r="E142" s="5" t="n"/>
-      <c r="F142" s="5" t="n"/>
-      <c r="G142" s="5" t="n"/>
-      <c r="H142" s="5" t="n"/>
-      <c r="I142" s="5" t="n"/>
-      <c r="J142" s="6" t="n"/>
-      <c r="K142" s="5" t="n"/>
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Jaineel Patel</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>jaineel.patel@genzeon.com</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jaineel-patel</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Genzeon</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L142" s="5" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n"/>
-      <c r="B143" s="5" t="n"/>
-      <c r="C143" s="5" t="n"/>
-      <c r="D143" s="5" t="n"/>
-      <c r="E143" s="5" t="n"/>
-      <c r="F143" s="5" t="n"/>
-      <c r="G143" s="5" t="n"/>
-      <c r="H143" s="5" t="n"/>
-      <c r="I143" s="5" t="n"/>
-      <c r="J143" s="6" t="n"/>
-      <c r="K143" s="5" t="n"/>
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Ruchita Kolla</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>kolla.ruchita@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ruchita-kolla</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K143" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L143" s="5" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n"/>
-      <c r="B144" s="5" t="n"/>
-      <c r="C144" s="5" t="n"/>
-      <c r="D144" s="5" t="n"/>
-      <c r="E144" s="5" t="n"/>
-      <c r="F144" s="5" t="n"/>
-      <c r="G144" s="5" t="n"/>
-      <c r="H144" s="5" t="n"/>
-      <c r="I144" s="5" t="n"/>
-      <c r="J144" s="6" t="n"/>
-      <c r="K144" s="5" t="n"/>
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Amey Dalvi</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>amey.dalvi@teamcomputers.com</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/amey-dalvi-07504b131</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>PreSales Consultant</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Team Computers</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L144" s="5" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n"/>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="5" t="n"/>
-      <c r="E145" s="5" t="n"/>
-      <c r="F145" s="5" t="n"/>
-      <c r="G145" s="5" t="n"/>
-      <c r="H145" s="5" t="n"/>
-      <c r="I145" s="5" t="n"/>
-      <c r="J145" s="6" t="n"/>
-      <c r="K145" s="5" t="n"/>
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Dushyant Shah</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>dushyant.shah@appstrail.com</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dushyantshahpm</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Appstrail Technology</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L145" s="5" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n"/>
-      <c r="B146" s="5" t="n"/>
-      <c r="C146" s="5" t="n"/>
-      <c r="D146" s="5" t="n"/>
-      <c r="E146" s="5" t="n"/>
-      <c r="F146" s="5" t="n"/>
-      <c r="G146" s="5" t="n"/>
-      <c r="H146" s="5" t="n"/>
-      <c r="I146" s="5" t="n"/>
-      <c r="J146" s="6" t="n"/>
-      <c r="K146" s="5" t="n"/>
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Pranshur Dubey</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>pranshur.d@qbotica.com</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/pranshurdubey</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>qBotica</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L146" s="5" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n"/>
-      <c r="B147" s="5" t="n"/>
-      <c r="C147" s="5" t="n"/>
-      <c r="D147" s="5" t="n"/>
-      <c r="E147" s="5" t="n"/>
-      <c r="F147" s="5" t="n"/>
-      <c r="G147" s="5" t="n"/>
-      <c r="H147" s="5" t="n"/>
-      <c r="I147" s="5" t="n"/>
-      <c r="J147" s="6" t="n"/>
-      <c r="K147" s="5" t="n"/>
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Kamya Batra</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>kbatra@eworkplaceapps.com</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/kamya-batra-3962ba220</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>eWorkplace Apps</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L147" s="5" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n"/>
-      <c r="B148" s="5" t="n"/>
-      <c r="C148" s="5" t="n"/>
-      <c r="D148" s="5" t="n"/>
-      <c r="E148" s="5" t="n"/>
-      <c r="F148" s="5" t="n"/>
-      <c r="G148" s="5" t="n"/>
-      <c r="H148" s="5" t="n"/>
-      <c r="I148" s="5" t="n"/>
-      <c r="J148" s="6" t="n"/>
-      <c r="K148" s="5" t="n"/>
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Shantanu Kulkarni</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>shantanu.k@autoplant.in</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shantanu-kulkarni-53506325</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Autoplant System India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L148" s="5" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n"/>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="5" t="n"/>
-      <c r="D149" s="5" t="n"/>
-      <c r="E149" s="5" t="n"/>
-      <c r="F149" s="5" t="n"/>
-      <c r="G149" s="5" t="n"/>
-      <c r="H149" s="5" t="n"/>
-      <c r="I149" s="5" t="n"/>
-      <c r="J149" s="6" t="n"/>
-      <c r="K149" s="5" t="n"/>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Priya Panchal</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>priya.panchal@mewurk.com</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/priya-panchal-8a1947292</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Mewurk HR</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L149" s="5" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="5" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="n"/>
-      <c r="E150" s="5" t="n"/>
-      <c r="F150" s="5" t="n"/>
-      <c r="G150" s="5" t="n"/>
-      <c r="H150" s="5" t="n"/>
-      <c r="I150" s="5" t="n"/>
-      <c r="J150" s="6" t="n"/>
-      <c r="K150" s="5" t="n"/>
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Mohammad Shoaib</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>mohammad.shoaib@sotiotech.com</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/mohammad-shoaib-408b45245</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Sotiotech</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L150" s="5" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n"/>
-      <c r="B151" s="5" t="n"/>
-      <c r="C151" s="5" t="n"/>
-      <c r="D151" s="5" t="n"/>
-      <c r="E151" s="5" t="n"/>
-      <c r="F151" s="5" t="n"/>
-      <c r="G151" s="5" t="n"/>
-      <c r="H151" s="5" t="n"/>
-      <c r="I151" s="5" t="n"/>
-      <c r="J151" s="6" t="n"/>
-      <c r="K151" s="5" t="n"/>
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Shubham Tyagi</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>shubham.tyagi@wipro.com</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/imshubhamtyagi</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="n"/>
-      <c r="B152" s="5" t="n"/>
-      <c r="C152" s="5" t="n"/>
-      <c r="D152" s="5" t="n"/>
-      <c r="E152" s="5" t="n"/>
-      <c r="F152" s="5" t="n"/>
-      <c r="G152" s="5" t="n"/>
-      <c r="H152" s="5" t="n"/>
-      <c r="I152" s="5" t="n"/>
-      <c r="J152" s="6" t="n"/>
-      <c r="K152" s="5" t="n"/>
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Madhukar Km</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>mkm@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/madhukar-km</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L152" s="5" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n"/>
-      <c r="B153" s="5" t="n"/>
-      <c r="C153" s="5" t="n"/>
-      <c r="D153" s="5" t="n"/>
-      <c r="E153" s="5" t="n"/>
-      <c r="F153" s="5" t="n"/>
-      <c r="G153" s="5" t="n"/>
-      <c r="H153" s="5" t="n"/>
-      <c r="I153" s="5" t="n"/>
-      <c r="J153" s="6" t="n"/>
-      <c r="K153" s="5" t="n"/>
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Kundan Pathak</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>kundan.pathak@cognizant.com</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/kundan-pathak</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L153" s="5" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n"/>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="5" t="n"/>
-      <c r="E154" s="5" t="n"/>
-      <c r="F154" s="5" t="n"/>
-      <c r="G154" s="5" t="n"/>
-      <c r="H154" s="5" t="n"/>
-      <c r="I154" s="5" t="n"/>
-      <c r="J154" s="6" t="n"/>
-      <c r="K154" s="5" t="n"/>
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Pratul Roy</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>pratul.roy@nagarro.com</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/pratul-roy-54869415a</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Nagarro</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L154" s="5" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n"/>
-      <c r="B155" s="5" t="n"/>
-      <c r="C155" s="5" t="n"/>
-      <c r="D155" s="5" t="n"/>
-      <c r="E155" s="5" t="n"/>
-      <c r="F155" s="5" t="n"/>
-      <c r="G155" s="5" t="n"/>
-      <c r="H155" s="5" t="n"/>
-      <c r="I155" s="5" t="n"/>
-      <c r="J155" s="6" t="n"/>
-      <c r="K155" s="5" t="n"/>
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Ayush Srivastava</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>ayush.srivastava@essindia.com</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ayush-srivastava-914136229</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Eastern Software Solutions</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L155" s="5" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n"/>
-      <c r="B156" s="5" t="n"/>
-      <c r="C156" s="5" t="n"/>
-      <c r="D156" s="5" t="n"/>
-      <c r="E156" s="5" t="n"/>
-      <c r="F156" s="5" t="n"/>
-      <c r="G156" s="5" t="n"/>
-      <c r="H156" s="5" t="n"/>
-      <c r="I156" s="5" t="n"/>
-      <c r="J156" s="6" t="n"/>
-      <c r="K156" s="5" t="n"/>
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Shubhangi Srivastava</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>shubhangis@vastedge.com</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/shubhangi-srivastava-b3b0331b5</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Vast Edge Cloud Backup, Apps</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L156" s="5" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="n"/>
-      <c r="B157" s="5" t="n"/>
-      <c r="C157" s="5" t="n"/>
-      <c r="D157" s="5" t="n"/>
-      <c r="E157" s="5" t="n"/>
-      <c r="F157" s="5" t="n"/>
-      <c r="G157" s="5" t="n"/>
-      <c r="H157" s="5" t="n"/>
-      <c r="I157" s="5" t="n"/>
-      <c r="J157" s="6" t="n"/>
-      <c r="K157" s="5" t="n"/>
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Anwesha Banerjee</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>anwesha.banerjee@hcltech.com</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/anwesha-banerjee-baa503205</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L157" s="5" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n"/>
-      <c r="B158" s="5" t="n"/>
-      <c r="C158" s="5" t="n"/>
-      <c r="D158" s="5" t="n"/>
-      <c r="E158" s="5" t="n"/>
-      <c r="F158" s="5" t="n"/>
-      <c r="G158" s="5" t="n"/>
-      <c r="H158" s="5" t="n"/>
-      <c r="I158" s="5" t="n"/>
-      <c r="J158" s="6" t="n"/>
-      <c r="K158" s="5" t="n"/>
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>Vaishnavi Kumbhar</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>vaishnavi.kumbhar@accenture.com</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/vaishnavi-kumbhar-7306b2250</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L158" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="n"/>
-      <c r="B159" s="5" t="n"/>
-      <c r="C159" s="5" t="n"/>
-      <c r="D159" s="5" t="n"/>
-      <c r="E159" s="5" t="n"/>
-      <c r="F159" s="5" t="n"/>
-      <c r="G159" s="5" t="n"/>
-      <c r="H159" s="5" t="n"/>
-      <c r="I159" s="5" t="n"/>
-      <c r="J159" s="6" t="n"/>
-      <c r="K159" s="5" t="n"/>
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Parv Bansal</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>parv.bansal@wipro.com</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/bansal-parv</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L159" s="5" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n"/>
-      <c r="B160" s="5" t="n"/>
-      <c r="C160" s="5" t="n"/>
-      <c r="D160" s="5" t="n"/>
-      <c r="E160" s="5" t="n"/>
-      <c r="F160" s="5" t="n"/>
-      <c r="G160" s="5" t="n"/>
-      <c r="H160" s="5" t="n"/>
-      <c r="I160" s="5" t="n"/>
-      <c r="J160" s="6" t="n"/>
-      <c r="K160" s="5" t="n"/>
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Jaden Toh</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>jaden.toh@alpha-sense.com</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jadentoh</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>AlphaSense</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L160" s="5" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n"/>
-      <c r="B161" s="5" t="n"/>
-      <c r="C161" s="5" t="n"/>
-      <c r="D161" s="5" t="n"/>
-      <c r="E161" s="5" t="n"/>
-      <c r="F161" s="5" t="n"/>
-      <c r="G161" s="5" t="n"/>
-      <c r="H161" s="5" t="n"/>
-      <c r="I161" s="5" t="n"/>
-      <c r="J161" s="6" t="n"/>
-      <c r="K161" s="5" t="n"/>
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Claire Kao</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>clairekao@bigobject.io</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/claire-ting-wei-kao-b74b1110b</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>BigObject Inc.</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K161" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L161" s="5" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n"/>
-      <c r="B162" s="5" t="n"/>
-      <c r="C162" s="5" t="n"/>
-      <c r="D162" s="5" t="n"/>
-      <c r="E162" s="5" t="n"/>
-      <c r="F162" s="5" t="n"/>
-      <c r="G162" s="5" t="n"/>
-      <c r="H162" s="5" t="n"/>
-      <c r="I162" s="5" t="n"/>
-      <c r="J162" s="6" t="n"/>
-      <c r="K162" s="5" t="n"/>
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Gracia Kwantalalu</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>gracia.kwantalalu@avepoint.com</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/gracia-yk</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>AvePoint</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J162" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L162" s="5" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="n"/>
-      <c r="B163" s="5" t="n"/>
-      <c r="C163" s="5" t="n"/>
-      <c r="D163" s="5" t="n"/>
-      <c r="E163" s="5" t="n"/>
-      <c r="F163" s="5" t="n"/>
-      <c r="G163" s="5" t="n"/>
-      <c r="H163" s="5" t="n"/>
-      <c r="I163" s="5" t="n"/>
-      <c r="J163" s="6" t="n"/>
-      <c r="K163" s="5" t="n"/>
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Wenxi Liu</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>wenxi.liu@quanthouse.com</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/wenxi-liu</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>QuantHouse</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K163" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L163" s="5" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="n"/>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="5" t="n"/>
-      <c r="D164" s="5" t="n"/>
-      <c r="E164" s="5" t="n"/>
-      <c r="F164" s="5" t="n"/>
-      <c r="G164" s="5" t="n"/>
-      <c r="H164" s="5" t="n"/>
-      <c r="I164" s="5" t="n"/>
-      <c r="J164" s="6" t="n"/>
-      <c r="K164" s="5" t="n"/>
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Joshua Aw</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>joshuaaw@mtechpro.com</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/joshua-aw-0a9634234</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>Presales Consultant</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>M.Tech</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>A1 - Presales</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>Apollo.io (manual web UI — user-uploaded file, not via manual_sourcing/ folder)</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L164" s="5" t="n"/>
     </row>
     <row r="165">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Business Development Representative role at REVEL | Renting de Coches</t>
+          <t>Hook: Saw your Sales Business Development Representative role at REVEL | Renting de Coches | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant role at o9 Solutions, Inc.</t>
+          <t>Hook: Saw your Presales Solutions Consultant role at o9 Solutions, Inc. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software</t>
+          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales - Solutions Consultant role at Earnix 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales - Solutions Consultant role at Earnix 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Solutions Consultant role at ORO Labs 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Solutions Consultant role at ORO Labs 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales and Solutions Consultant role at Aspire Systems 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales and Solutions Consultant role at Aspire Systems 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Columbus 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Columbus 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Tata Consultancy Services 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Tata Consultancy Services 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant, Bid Manager role at Orange Cyberdefense 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales Solutions Consultant, Bid Manager role at Orange Cyberdefense 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at Haiilo 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at Haiilo 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive / Sales Manager role at Storyly 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive / Sales Manager role at Storyly 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at TRUE LABS 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at TRUE LABS 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive &amp; Sales Manager role at Insure Smart Limited 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive &amp; Sales Manager role at Insure Smart Limited 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at CybExer Technologies 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at CybExer Technologies 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Consultant Manager role at V-Valley 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales Consultant Manager role at V-Valley 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager, Account Executive role at Alconost 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager, Account Executive role at Alconost 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Senior Presales Consultant &amp; Solutions Consultant role at Hexadroit Pvt. Ltd. 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Senior Presales Consultant &amp; Solutions Consultant role at Hexadroit Pvt. Ltd. 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Commercial Account Manager role at Boomi 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Commercial Account Manager role at Boomi 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at yoummday 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at yoummday 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive / Enterprise Sales role at Neeyamo 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive / Enterprise Sales role at Neeyamo 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager | Account Executive role at kununu 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager | Account Executive role at kununu 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager role at Dyad 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager role at Dyad 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive | Sales Manager role at Muck Rack 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive | Sales Manager role at Muck Rack 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="R53" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager - Account Executive role at Arivo 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager - Account Executive role at Arivo 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager - Account Executive role at UPTOO 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager - Account Executive role at UPTOO 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="R55" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your SAP Partner Sales Manager &amp; Enterprise Account Executive role at EPI-USE Labs 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your SAP Partner Sales Manager &amp; Enterprise Account Executive role at EPI-USE Labs 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="R56" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager &amp; Account Executive role at Dyad 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager &amp; Account Executive role at Dyad 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="R57" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at Tellimer 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at Tellimer 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="R58" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Enterprise Account Manager &amp; Sales Manager role at 42Gears 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Enterprise Account Manager &amp; Sales Manager role at 42Gears 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="R59" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Enterprise Sales Manager / Account Executive role at Anakin (YC S21) 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Enterprise Sales Manager / Account Executive role at Anakin (YC S21) 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="R60" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead role at adidas | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead role at adidas | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="R61" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Manager role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Manager role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="R62" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales &amp; Business Development Representative role at Zvolv | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales &amp; Business Development Representative role at Zvolv | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="R63" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative - Sales role at TopSource | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Business Development Representative - Sales role at TopSource | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at Atos | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Consultant role at Atos | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="R65" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at BT Group | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Consultant role at BT Group | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant - Delivery Lead role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant - Delivery Lead role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="R69" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant role at Northern Trust | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant role at Northern Trust | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="R70" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Executive role at Capgemini | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Executive role at Capgemini | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="R71" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative role at Insight | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Business Development Representative role at Insight | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="R73" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant Delivery-Lead role at Worldline Global Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant Delivery-Lead role at Worldline Global Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="R76" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at LHH | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at LHH | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="R77" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="R79" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Senior Delivery Manager role at EPAM Systems | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Senior Delivery Manager role at EPAM Systems | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="R80" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="R85" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="R87" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="R88" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="R89" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="R90" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="R92" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="R94" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="R95" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="R96" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="R97" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Service Delivery Manager role at V &amp; V Comptech Systems Private Limited | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Service Delivery Manager role at V &amp; V Comptech Systems Private Limited | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="R98" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="R99" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="R101" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="R104" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="R105" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="R108" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Consultant role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="R109" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Manager (Consultant) - Senior Delivery Lead role at Burendo | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Manager (Consultant) - Senior Delivery Lead role at Burendo | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="R110" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Agile Delivery Manager role at tombola | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Agile Delivery Manager role at tombola | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="R111" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales and Business Development Representative role at Cygnus Group Ltd | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales and Business Development Representative role at Cygnus Group Ltd | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter announcement sent 2026-09-25 (LinkedIn newsletter promo: "Demo went perfectly, deal stalled anyway" + subscribe CTA) — one-off broadcast, not part of the 5-touch sequence.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -949,10 +949,12 @@
       <c r="N6" s="6" t="n"/>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>46293</v>
+      </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -960,7 +962,7 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Follow-up send bounced 2026-09-25: "Address not found" (mailer-daemon, 550 5.1.1). Sequence was already complete; marking Bounced for the record, no further email to be sent.</t>
         </is>
       </c>
     </row>
@@ -1322,10 +1324,12 @@
       <c r="N11" s="6" t="n"/>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>46293</v>
+      </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -1333,7 +1337,7 @@
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Follow-up send bounced 2026-09-25: "Address not found" (mailer-daemon). Sequence was already complete; marking Bounced for the record, no further email to be sent.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -949,10 +949,14 @@
       <c r="N6" s="6" t="n"/>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -960,7 +964,7 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Bounced 2026-09-25: address not found (mailer-daemon), detected via Gmail search on 2026-10-02 (Friday follow-up run). Has LinkedIn URL, left Stage/Next Action as-is.</t>
         </is>
       </c>
     </row>
@@ -1322,10 +1326,14 @@
       <c r="N11" s="6" t="n"/>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -1333,7 +1341,7 @@
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Bounced 2026-09-25: address not found (mailer-daemon), detected via Gmail search on 2026-10-02 (Friday follow-up run). Has LinkedIn URL, left Stage/Next Action as-is.</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Business Development Representative role at REVEL | Renting de Coches</t>
+          <t>Hook: Saw your Sales Business Development Representative role at REVEL | Renting de Coches | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant role at o9 Solutions, Inc.</t>
+          <t>Hook: Saw your Presales Solutions Consultant role at o9 Solutions, Inc. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software</t>
+          <t>Hook: Saw your Presales Solutions Consultant role at Siemens Digital Industries Software | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response.</t>
+          <t>Email 1 sent 2026-08-12 (retroactively logged from Gmail Sent folder — see run digest for context). 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales - Solutions Consultant role at Earnix 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales - Solutions Consultant role at Earnix 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Solutions Consultant role at ORO Labs 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Solutions Consultant role at ORO Labs 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales and Solutions Consultant role at Aspire Systems 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales and Solutions Consultant role at Aspire Systems 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Columbus 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Columbus 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Tata Consultancy Services 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales &amp; Solutions Consultant role at Tata Consultancy Services 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Solutions Consultant, Bid Manager role at Orange Cyberdefense 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales Solutions Consultant, Bid Manager role at Orange Cyberdefense 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at Haiilo 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at Haiilo 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive / Sales Manager role at Storyly 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive / Sales Manager role at Storyly 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive Sales Manager role at TRUE LABS 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive Sales Manager role at TRUE LABS 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive &amp; Sales Manager role at Insure Smart Limited 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive &amp; Sales Manager role at Insure Smart Limited 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at CybExer Technologies 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at CybExer Technologies 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Presales Consultant Manager role at V-Valley 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Presales Consultant Manager role at V-Valley 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager, Account Executive role at Alconost 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager, Account Executive role at Alconost 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Senior Presales Consultant &amp; Solutions Consultant role at Hexadroit Pvt. Ltd. 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Senior Presales Consultant &amp; Solutions Consultant role at Hexadroit Pvt. Ltd. 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Commercial Account Manager role at Boomi 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Commercial Account Manager role at Boomi 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at yoummday 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at yoummday 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive / Enterprise Sales role at Neeyamo 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive / Enterprise Sales role at Neeyamo 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager | Account Executive role at kununu 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager | Account Executive role at kununu 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager role at Dyad 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager role at Dyad 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Account Executive | Sales Manager role at Muck Rack 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Account Executive | Sales Manager role at Muck Rack 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="R53" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager - Account Executive role at Arivo 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager - Account Executive role at Arivo 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager - Account Executive role at UPTOO 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager - Account Executive role at UPTOO 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="R55" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your SAP Partner Sales Manager &amp; Enterprise Account Executive role at EPI-USE Labs 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your SAP Partner Sales Manager &amp; Enterprise Account Executive role at EPI-USE Labs 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="R56" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager &amp; Account Executive role at Dyad 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager &amp; Account Executive role at Dyad 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="R57" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales Manager / Account Executive role at Tellimer 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales Manager / Account Executive role at Tellimer 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="R58" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Enterprise Account Manager &amp; Sales Manager role at 42Gears 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Enterprise Account Manager &amp; Sales Manager role at 42Gears 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="R59" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Enterprise Sales Manager / Account Executive role at Anakin (YC S21) 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Enterprise Sales Manager / Account Executive role at Anakin (YC S21) 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="R60" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead role at adidas | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead role at adidas | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="R61" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Manager role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Manager role at DXC Technology | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="R62" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales &amp; Business Development Representative role at Zvolv | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales &amp; Business Development Representative role at Zvolv | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="R63" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative - Sales role at TopSource | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Business Development Representative - Sales role at TopSource | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at Atos | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Consultant role at Atos | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="R65" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at BT Group | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Consultant role at BT Group | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant - Delivery Lead role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant - Delivery Lead role at Tata Consultancy Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="R69" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant role at Northern Trust | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant role at Northern Trust | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="R70" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Executive role at Capgemini | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Executive role at Capgemini | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="R71" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Business Development Representative role at Insight | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Business Development Representative role at Insight | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="R73" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Consultant Delivery-Lead role at Worldline Global Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Consultant Delivery-Lead role at Worldline Global Services | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="R76" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at LHH | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at LHH | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="R77" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Delivery Consultant role at Vallum Associates | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="R79" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Senior Delivery Manager role at EPAM Systems | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Senior Delivery Manager role at EPAM Systems | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="R80" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="R85" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="R87" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="R88" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="R89" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="R90" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="R92" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="R94" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="R95" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="R96" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="R97" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Service Delivery Manager role at V &amp; V Comptech Systems Private Limited | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Service Delivery Manager role at V &amp; V Comptech Systems Private Limited | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="R98" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="R99" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="R101" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="R104" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="R105" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Lead Manager role at Accenture | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="R108" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Lead Consultant role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Lead Consultant role at Infosys | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="R109" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Delivery Manager (Consultant) - Senior Delivery Lead role at Burendo | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Delivery Manager (Consultant) - Senior Delivery Lead role at Burendo | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="R110" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Agile Delivery Manager role at tombola | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Agile Delivery Manager role at tombola | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="R111" s="5" t="inlineStr">
         <is>
-          <t>Hook: Saw your Sales and Business Development Representative role at Cygnus Group Ltd | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response.</t>
+          <t>Hook: Saw your Sales and Business Development Representative role at Cygnus Group Ltd | Sourced via Apollo.io web UI (API blocked on abhisri2686 trial plan; manually browsed and exported to Excel 2026-08-31) | 5-touch sequence complete, no response. | Newsletter sent 2026-10-08: demo-trust-framework article (https://lnkd.in/p/ev8ZGf-B).</t>
         </is>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8725,7 +8725,7 @@
       </c>
       <c r="R112" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000</t>
+          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="R113" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000</t>
+          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="R114" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000</t>
+          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="R115" s="18" t="inlineStr">
         <is>
-          <t>Saw your PreSales Consultant role at Team Computers | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 5500</t>
+          <t>Saw your PreSales Consultant role at Team Computers | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 5500 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R116" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Indictrans | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 100</t>
+          <t>Saw your Presales Consultant role at Indictrans | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 100 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="R117" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Infosys | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 328000</t>
+          <t>Saw your Presales Consultant role at Infosys | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 328000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="R118" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Accenture | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 799000</t>
+          <t>Saw your Presales Consultant role at Accenture | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 799000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="R121" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at MetricStream | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 1300</t>
+          <t>Saw your Presales Consultant role at MetricStream | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 1300 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R122" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Nagarro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 19000</t>
+          <t>Saw your Presales Consultant role at Nagarro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 19000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="R123" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Eastern Software Solutions | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 630</t>
+          <t>Saw your Presales Consultant role at Eastern Software Solutions | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 630 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="R124" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Cognizant | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 357000</t>
+          <t>Saw your Presales Consultant role at Cognizant | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 357000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="R125" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Sotiotech | Go-To ServiceNow Partner | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 49</t>
+          <t>Saw your Presales Consultant role at Sotiotech | Go-To ServiceNow Partner | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 49 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="R126" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Veefin | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 290</t>
+          <t>Saw your Presales Consultant role at Veefin | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 290 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="R127" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Valuehub | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 180</t>
+          <t>Saw your Presales Consultant role at Valuehub | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 180 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="R128" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Tecnotree Corporation | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 760</t>
+          <t>Saw your Presales Consultant role at Tecnotree Corporation | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 760 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="R129" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Cyfuture | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 5000</t>
+          <t>Saw your Presales Consultant role at Cyfuture | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 5000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="R130" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Autoplant System India Pvt. Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 350</t>
+          <t>Saw your Presales Consultant role at Autoplant System India Pvt. Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 350 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="R131" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at L&amp;T Technology Services | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 22000</t>
+          <t>Saw your Presales Consultant role at L&amp;T Technology Services | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 22000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="R132" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Autoplant System India Pvt. Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 350</t>
+          <t>Saw your Presales Consultant role at Autoplant System India Pvt. Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 350 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="R133" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Execo | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 500</t>
+          <t>Saw your Presales Consultant role at Execo | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 500 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="R134" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at qBotica | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 200</t>
+          <t>Saw your Presales Consultant role at qBotica | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 200 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="R135" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000</t>
+          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="R136" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at PTR Global | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 260</t>
+          <t>Saw your Presales Consultant role at PTR Global | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 260 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="R137" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Vast Edge Cloud Backup, Apps | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 60</t>
+          <t>Saw your Presales Consultant role at Vast Edge Cloud Backup, Apps | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 60 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="R138" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Wipro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 240000</t>
+          <t>Saw your Presales Consultant role at Wipro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 240000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="R139" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Wipro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 240000</t>
+          <t>Saw your Presales Consultant role at Wipro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 240000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="R140" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Solytics Partners | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 430</t>
+          <t>Saw your Presales Consultant role at Solytics Partners | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 430 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="R141" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Infojini Inc | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 950</t>
+          <t>Saw your Presales Consultant role at Infojini Inc | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 950 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="R143" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Capgemini | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 423000</t>
+          <t>Saw your Presales Consultant role at Capgemini | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 423000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="R144" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Wipro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 240000</t>
+          <t>Saw your Presales Consultant role at Wipro | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 240000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="R145" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000</t>
+          <t>Saw your Presales Consultant role at HCLTech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 234000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="R146" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Genpact | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 141000</t>
+          <t>Saw your Presales Consultant role at Genpact | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 141000 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="R147" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Swan Solutions &amp; Services Pvt Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 250</t>
+          <t>Saw your Presales Consultant role at Swan Solutions &amp; Services Pvt Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 250 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11341,7 +11341,7 @@
       </c>
       <c r="R148" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Solytics Partners | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 430</t>
+          <t>Saw your Presales Consultant role at Solytics Partners | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 430 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="R149" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Prospecta Software | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 380</t>
+          <t>Saw your Presales Consultant role at Prospecta Software | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 380 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="R150" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Incite Gravity | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 38</t>
+          <t>Saw your Presales Consultant role at Incite Gravity | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 38 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="R151" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Genzeon | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 670</t>
+          <t>Saw your Presales Consultant role at Genzeon | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 670 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="R152" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at eWorkplace Apps | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 75</t>
+          <t>Saw your Presales Consultant role at eWorkplace Apps | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 75 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="R153" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Photon | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 7500</t>
+          <t>Saw your Presales Consultant role at Photon | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 7500 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="R154" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at Thinkinnov Solution Technologies Private Limited | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 120</t>
+          <t>Saw your Presales Consultant role at Thinkinnov Solution Technologies Private Limited | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 120 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="R155" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at iONE IT Solutions Pvt. Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 62</t>
+          <t>Saw your Presales Consultant role at iONE IT Solutions Pvt. Ltd. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 62 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="R195" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at AlphaSense | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 3800</t>
+          <t>Saw your Presales Consultant role at AlphaSense | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 3800 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="R196" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at M.Tech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 600</t>
+          <t>Saw your Presales Consultant role at M.Tech | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 600 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="R197" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at AvePoint | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 3500</t>
+          <t>Saw your Presales Consultant role at AvePoint | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 3500 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="R198" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at QuantHouse | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 87</t>
+          <t>Saw your Presales Consultant role at QuantHouse | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 87 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="R199" s="18" t="inlineStr">
         <is>
-          <t>Saw your Presales Consultant role at BigObject Inc. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 28</t>
+          <t>Saw your Presales Consultant role at BigObject Inc. | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 28 | Newsletter sent 2026-10-23: "AI just did my least favorite part of presales" (LinkedIn article), with newsletter-subscribe and profile-follow links included.</t>
         </is>
       </c>
     </row>
@@ -14982,36 +14982,36 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="11" t="inlineStr">
         <is>
           <t>Geoffrey Hernandez</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C201" s="11" t="inlineStr">
         <is>
           <t>http://www.linkedin.com/in/geoffrey-h-99602123</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D201" s="11" t="inlineStr">
         <is>
           <t>Apollo.io</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E201" s="11" t="inlineStr">
         <is>
           <t>Sales &amp; Presales Career Progression</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F201" s="11" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="H201">
+      <c r="H201" s="11">
         <f>IF(G201="","",TODAY()-G201)</f>
         <v/>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I201" s="11" t="inlineStr">
         <is>
           <t>Send LinkedIn Connection Request</t>
         </is>
@@ -15019,63 +15019,63 @@
       <c r="J201" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
+      <c r="K201" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M201" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O201" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q201" s="11" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="R201" t="inlineStr">
+      <c r="R201" s="11" t="inlineStr">
         <is>
           <t>Saw your Presales Consultant role at Crayon | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 2700</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="11" t="inlineStr">
         <is>
           <t>Pulkit Agarwal</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C202" s="11" t="inlineStr">
         <is>
           <t>http://www.linkedin.com/in/pulkit4501</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D202" s="11" t="inlineStr">
         <is>
           <t>Apollo.io</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E202" s="11" t="inlineStr">
         <is>
           <t>Sales &amp; Presales Career Progression</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F202" s="11" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="H202">
+      <c r="H202" s="11">
         <f>IF(G202="","",TODAY()-G202)</f>
         <v/>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I202" s="11" t="inlineStr">
         <is>
           <t>Send LinkedIn Connection Request</t>
         </is>
@@ -15083,63 +15083,63 @@
       <c r="J202" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
+      <c r="K202" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M202" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O202" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q202" s="11" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="R202" t="inlineStr">
+      <c r="R202" s="11" t="inlineStr">
         <is>
           <t>Saw your Presales Consultant role at Slimstock | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 600</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="11" t="inlineStr">
         <is>
           <t>Juan Teo</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C203" s="11" t="inlineStr">
         <is>
           <t>http://www.linkedin.com/in/teojuansiew</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" s="11" t="inlineStr">
         <is>
           <t>Apollo.io</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E203" s="11" t="inlineStr">
         <is>
           <t>Sales &amp; Presales Career Progression</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F203" s="11" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="H203">
+      <c r="H203" s="11">
         <f>IF(G203="","",TODAY()-G203)</f>
         <v/>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I203" s="11" t="inlineStr">
         <is>
           <t>Send LinkedIn Connection Request</t>
         </is>
@@ -15147,63 +15147,63 @@
       <c r="J203" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
+      <c r="K203" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M203" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O203" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q203" s="11" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="R203" t="inlineStr">
+      <c r="R203" s="11" t="inlineStr">
         <is>
           <t>Saw your Presales Consultant role at Elixir Technology | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 51</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="11" t="inlineStr">
         <is>
           <t>Sibikrishnan</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C204" s="11" t="inlineStr">
         <is>
           <t>http://www.linkedin.com/in/agsibikrishnan</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D204" s="11" t="inlineStr">
         <is>
           <t>Apollo.io</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E204" s="11" t="inlineStr">
         <is>
           <t>Sales &amp; Presales Career Progression</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F204" s="11" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="H204">
+      <c r="H204" s="11">
         <f>IF(G204="","",TODAY()-G204)</f>
         <v/>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I204" s="11" t="inlineStr">
         <is>
           <t>Send LinkedIn Connection Request</t>
         </is>
@@ -15211,63 +15211,63 @@
       <c r="J204" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
+      <c r="K204" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M204" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O204" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q204" s="11" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="R204" t="inlineStr">
+      <c r="R204" s="11" t="inlineStr">
         <is>
           <t>Saw your Presales Consultant role at Jeen.ai | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 140</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="11" t="inlineStr">
         <is>
           <t>Betty Jiun</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C205" s="11" t="inlineStr">
         <is>
           <t>http://www.linkedin.com/in/betty-tan-rou-jiun-21369b137</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D205" s="11" t="inlineStr">
         <is>
           <t>Apollo.io</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E205" s="11" t="inlineStr">
         <is>
           <t>Sales &amp; Presales Career Progression</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F205" s="11" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="H205">
+      <c r="H205" s="11">
         <f>IF(G205="","",TODAY()-G205)</f>
         <v/>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I205" s="11" t="inlineStr">
         <is>
           <t>Send LinkedIn Connection Request</t>
         </is>
@@ -15275,27 +15275,27 @@
       <c r="J205" s="23" t="n">
         <v>46318</v>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr">
+      <c r="K205" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M205" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O205" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q205" s="11" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="R205" t="inlineStr">
+      <c r="R205" s="11" t="inlineStr">
         <is>
           <t>Saw your Presales Consultant role at 1CLOUDSTAR | Sourced via Apollo.io web UI (manual export; expanded geography incl. US/UK/Australia/Canada per Abhineet's 2026-10-23 approval) | Company size: 19</t>
         </is>
